--- a/supremelending/src/main/resources/SupremeLIONLOPLOSData.xlsx
+++ b/supremelending/src/main/resources/SupremeLIONLOPLOSData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hima/Documents/SeleniumProjects/SupremeLION_LOP_LOS_Hima/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\clientautomationscript\supremelending\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDBF1C1-FDBF-DB4C-8824-BDB6A648EC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A8C53C-06C5-4CB1-8663-08D7B4CA65B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="500" windowWidth="34780" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUP_LION_LOP_LOS" sheetId="9" r:id="rId1"/>
@@ -7375,9 +7375,6 @@
     <t>VA - Virginia</t>
   </si>
   <si>
-    <t>testusermobileapplication+qadsp+03@gmail.com</t>
-  </si>
-  <si>
     <t>04/01/1969</t>
   </si>
   <si>
@@ -7390,9 +7387,6 @@
     <t>12/15/1987</t>
   </si>
   <si>
-    <t>testusermobileapplication+qadsp+04@gmail.com</t>
-  </si>
-  <si>
     <t>testusermobileapplication+qadsp+05@gmail.com</t>
   </si>
   <si>
@@ -7411,9 +7405,6 @@
     <t>12/08/1959</t>
   </si>
   <si>
-    <t>testusermobileapplication+qadsp+12@gmail.com</t>
-  </si>
-  <si>
     <t>testusermobileapplication+qadsp+13@gmail.com</t>
   </si>
   <si>
@@ -7483,21 +7474,6 @@
     <t>testusermobileapplication+qadsp+18@gmail.com</t>
   </si>
   <si>
-    <t>testusermobileapplication+qadsp+19@gmail.com</t>
-  </si>
-  <si>
-    <t>testusermobileapplication+qadsp+20@gmail.com</t>
-  </si>
-  <si>
-    <t>testusermobileapplication+qadsp+21@gmail.com</t>
-  </si>
-  <si>
-    <t>testusermobileapplication+qadsp+22@gmail.com</t>
-  </si>
-  <si>
-    <t>testusermobileapplication+qadsp+23@gmail.com</t>
-  </si>
-  <si>
     <t>testusermobileapplication+qadsp+24@gmail.com</t>
   </si>
   <si>
@@ -7631,6 +7607,30 @@
   </si>
   <si>
     <t>Manufacutre/Mobile Home</t>
+  </si>
+  <si>
+    <t>testusermobileapplication+qa+03@gmail.com</t>
+  </si>
+  <si>
+    <t>testusermobileapplication+qa+04@gmail.com</t>
+  </si>
+  <si>
+    <t>testusermobileapplication+rsc40@gmail.com</t>
+  </si>
+  <si>
+    <t>testusermobileapplication+r40joseph_sc22@gmail.com</t>
+  </si>
+  <si>
+    <t>testusermobileapplication+r40lucius_sc21@gmail.com</t>
+  </si>
+  <si>
+    <t>testusermobileapplication+r40christopher_sc2o@gmail.com</t>
+  </si>
+  <si>
+    <t>testusermobileapplication+r40rodriguez_sc18@gmail.com</t>
+  </si>
+  <si>
+    <t>testusermobileapplication+r40fowler_sc12@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -7638,9 +7638,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7912,14 +7912,6 @@
       <name val="Cambria"/>
       <family val="1"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -8232,7 +8224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="264">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -8599,49 +8591,41 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="26" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="26" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="26" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="26" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="26" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="38" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="39" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="39" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="39" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="39" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8650,37 +8634,25 @@
     <xf numFmtId="0" fontId="39" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="39" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="39" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="39" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="39" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="39" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="42" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="41" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="26" fillId="16" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="26" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9015,62 +8987,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5DBE1D5-C161-7A4D-81F0-A5177D9D536D}">
   <dimension ref="A1:CK28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" style="137" customWidth="1"/>
-    <col min="2" max="2" width="57.1640625" style="137" customWidth="1"/>
+    <col min="1" max="1" width="24.109375" style="137" customWidth="1"/>
+    <col min="2" max="2" width="57.109375" style="137" customWidth="1"/>
     <col min="3" max="5" width="13.6640625" style="137" customWidth="1"/>
-    <col min="6" max="6" width="17.5" style="137" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" style="137" customWidth="1"/>
     <col min="7" max="7" width="20.33203125" style="137" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="137" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" style="137" customWidth="1"/>
     <col min="9" max="9" width="16" style="137" customWidth="1"/>
     <col min="10" max="10" width="22.6640625" style="137" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="137" customWidth="1"/>
-    <col min="12" max="12" width="30.83203125" style="137" customWidth="1"/>
-    <col min="13" max="13" width="13.83203125" style="137" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" style="137" customWidth="1"/>
+    <col min="12" max="12" width="30.77734375" style="137" customWidth="1"/>
+    <col min="13" max="13" width="13.77734375" style="137" customWidth="1"/>
     <col min="14" max="14" width="16.6640625" style="137" customWidth="1"/>
-    <col min="15" max="15" width="18.83203125" style="137" customWidth="1"/>
-    <col min="16" max="16" width="28.1640625" style="137" customWidth="1"/>
-    <col min="17" max="17" width="15.83203125" style="137" customWidth="1"/>
+    <col min="15" max="15" width="18.77734375" style="137" customWidth="1"/>
+    <col min="16" max="16" width="28.109375" style="137" customWidth="1"/>
+    <col min="17" max="17" width="15.77734375" style="137" customWidth="1"/>
     <col min="18" max="32" width="14.6640625" style="137" customWidth="1"/>
-    <col min="33" max="33" width="25.83203125" style="137" customWidth="1"/>
+    <col min="33" max="33" width="25.77734375" style="137" customWidth="1"/>
     <col min="34" max="35" width="14.6640625" style="137" customWidth="1"/>
-    <col min="36" max="37" width="20.5" style="137" customWidth="1"/>
-    <col min="38" max="39" width="18.1640625" style="137" customWidth="1"/>
-    <col min="40" max="40" width="16.83203125" style="137" customWidth="1"/>
+    <col min="36" max="37" width="20.44140625" style="137" customWidth="1"/>
+    <col min="38" max="39" width="18.109375" style="137" customWidth="1"/>
+    <col min="40" max="40" width="16.77734375" style="137" customWidth="1"/>
     <col min="41" max="41" width="24.33203125" style="137" customWidth="1"/>
-    <col min="42" max="42" width="12.5" style="137" customWidth="1"/>
-    <col min="43" max="43" width="25.5" style="137" customWidth="1"/>
-    <col min="44" max="44" width="12.5" style="137" customWidth="1"/>
+    <col min="42" max="42" width="12.44140625" style="137" customWidth="1"/>
+    <col min="43" max="43" width="25.44140625" style="137" customWidth="1"/>
+    <col min="44" max="44" width="12.44140625" style="137" customWidth="1"/>
     <col min="45" max="45" width="37.33203125" style="137" customWidth="1"/>
     <col min="46" max="46" width="49.33203125" style="137" customWidth="1"/>
-    <col min="47" max="47" width="39.5" style="137" customWidth="1"/>
-    <col min="48" max="48" width="27.83203125" style="137" customWidth="1"/>
-    <col min="49" max="49" width="32.5" style="226" customWidth="1"/>
-    <col min="50" max="50" width="35.5" style="137" customWidth="1"/>
-    <col min="51" max="54" width="8.83203125" style="137"/>
-    <col min="55" max="56" width="28.5" style="137" customWidth="1"/>
+    <col min="47" max="47" width="39.44140625" style="137" customWidth="1"/>
+    <col min="48" max="48" width="27.77734375" style="137" customWidth="1"/>
+    <col min="49" max="49" width="32.44140625" style="223" customWidth="1"/>
+    <col min="50" max="50" width="35.44140625" style="137" customWidth="1"/>
+    <col min="51" max="54" width="8.77734375" style="137"/>
+    <col min="55" max="56" width="28.44140625" style="137" customWidth="1"/>
     <col min="57" max="57" width="33.6640625" style="137" customWidth="1"/>
-    <col min="58" max="58" width="27.5" style="137" customWidth="1"/>
-    <col min="59" max="59" width="30.5" style="137" customWidth="1"/>
-    <col min="60" max="61" width="21.5" style="137" customWidth="1"/>
-    <col min="62" max="62" width="21.5" style="188" customWidth="1"/>
-    <col min="63" max="63" width="21.5" style="137" customWidth="1"/>
-    <col min="64" max="64" width="21.5" style="193" customWidth="1"/>
-    <col min="65" max="65" width="21.5" style="137" customWidth="1"/>
-    <col min="66" max="66" width="22.1640625" style="137" customWidth="1"/>
-    <col min="67" max="68" width="8.83203125" style="137"/>
-    <col min="69" max="69" width="13.1640625" style="137" customWidth="1"/>
-    <col min="70" max="82" width="8.83203125" style="137"/>
-    <col min="83" max="84" width="15.1640625" style="137" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" style="137" customWidth="1"/>
-    <col min="86" max="87" width="8.83203125" style="137"/>
-    <col min="88" max="88" width="18.83203125" style="137" customWidth="1"/>
-    <col min="89" max="89" width="54.83203125" style="137" customWidth="1"/>
-    <col min="90" max="16384" width="8.83203125" style="137"/>
+    <col min="58" max="58" width="27.44140625" style="137" customWidth="1"/>
+    <col min="59" max="59" width="30.44140625" style="137" customWidth="1"/>
+    <col min="60" max="61" width="21.44140625" style="137" customWidth="1"/>
+    <col min="62" max="62" width="21.44140625" style="188" customWidth="1"/>
+    <col min="63" max="63" width="21.44140625" style="137" customWidth="1"/>
+    <col min="64" max="64" width="21.44140625" style="193" customWidth="1"/>
+    <col min="65" max="65" width="21.44140625" style="137" customWidth="1"/>
+    <col min="66" max="66" width="22.109375" style="137" customWidth="1"/>
+    <col min="67" max="68" width="8.77734375" style="137"/>
+    <col min="69" max="69" width="13.109375" style="137" customWidth="1"/>
+    <col min="70" max="82" width="8.77734375" style="137"/>
+    <col min="83" max="84" width="15.109375" style="137" customWidth="1"/>
+    <col min="85" max="85" width="16.109375" style="137" customWidth="1"/>
+    <col min="86" max="87" width="8.77734375" style="137"/>
+    <col min="88" max="88" width="18.77734375" style="137" customWidth="1"/>
+    <col min="89" max="89" width="54.77734375" style="137" customWidth="1"/>
+    <col min="90" max="16384" width="8.77734375" style="137"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:89" s="134" customFormat="1" ht="17" thickBot="1">
+    <row r="1" spans="1:89" s="134" customFormat="1" ht="15.6" thickBot="1">
       <c r="A1" s="123" t="s">
         <v>1633</v>
       </c>
@@ -9125,29 +9097,29 @@
       <c r="R1" s="127" t="s">
         <v>1584</v>
       </c>
-      <c r="S1" s="257" t="s">
-        <v>2524</v>
-      </c>
-      <c r="T1" s="257" t="s">
-        <v>2525</v>
-      </c>
-      <c r="U1" s="257" t="s">
-        <v>2526</v>
-      </c>
-      <c r="V1" s="257" t="s">
-        <v>2527</v>
-      </c>
-      <c r="W1" s="257" t="s">
+      <c r="S1" s="241" t="s">
+        <v>2516</v>
+      </c>
+      <c r="T1" s="241" t="s">
+        <v>2517</v>
+      </c>
+      <c r="U1" s="241" t="s">
+        <v>2518</v>
+      </c>
+      <c r="V1" s="241" t="s">
+        <v>2519</v>
+      </c>
+      <c r="W1" s="241" t="s">
         <v>1538</v>
       </c>
-      <c r="X1" s="257" t="s">
-        <v>2528</v>
-      </c>
-      <c r="Y1" s="257" t="s">
-        <v>2531</v>
-      </c>
-      <c r="Z1" s="257" t="s">
-        <v>2529</v>
+      <c r="X1" s="241" t="s">
+        <v>2520</v>
+      </c>
+      <c r="Y1" s="241" t="s">
+        <v>2523</v>
+      </c>
+      <c r="Z1" s="241" t="s">
+        <v>2521</v>
       </c>
       <c r="AA1" s="129" t="s">
         <v>1613</v>
@@ -9215,23 +9187,23 @@
       <c r="AV1" s="129" t="s">
         <v>1594</v>
       </c>
-      <c r="AW1" s="221" t="s">
+      <c r="AW1" s="218" t="s">
         <v>1595</v>
       </c>
       <c r="AX1" s="129" t="s">
         <v>1596</v>
       </c>
       <c r="AY1" s="129" t="s">
+        <v>2476</v>
+      </c>
+      <c r="AZ1" s="129" t="s">
+        <v>2477</v>
+      </c>
+      <c r="BA1" s="129" t="s">
+        <v>2478</v>
+      </c>
+      <c r="BB1" s="129" t="s">
         <v>2479</v>
-      </c>
-      <c r="AZ1" s="129" t="s">
-        <v>2480</v>
-      </c>
-      <c r="BA1" s="129" t="s">
-        <v>2481</v>
-      </c>
-      <c r="BB1" s="129" t="s">
-        <v>2482</v>
       </c>
       <c r="BC1" s="127" t="s">
         <v>1603</v>
@@ -9339,12 +9311,12 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="2" spans="1:89" ht="52" thickBot="1">
+    <row r="2" spans="1:89" ht="46.8" thickBot="1">
       <c r="A2" s="135" t="s">
         <v>1663</v>
       </c>
-      <c r="B2" s="214" t="s">
-        <v>2497</v>
+      <c r="B2" s="213" t="s">
+        <v>2489</v>
       </c>
       <c r="C2" s="137" t="s">
         <v>3</v>
@@ -9373,36 +9345,31 @@
       <c r="K2" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="260"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="260"/>
-      <c r="O2" s="260"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="217"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="258" t="s">
+      <c r="Q2" s="140"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="242" t="s">
         <v>1670</v>
       </c>
-      <c r="T2" s="258" t="s">
+      <c r="T2" s="242" t="s">
         <v>1672</v>
       </c>
-      <c r="U2" s="262" t="s">
+      <c r="U2" s="244" t="s">
         <v>2412</v>
       </c>
       <c r="V2" s="141">
         <v>99507</v>
       </c>
-      <c r="W2" s="259" t="s">
+      <c r="W2" s="243" t="s">
         <v>5</v>
       </c>
       <c r="X2" s="141" t="s">
         <v>2302</v>
       </c>
-      <c r="Y2" s="263" t="s">
-        <v>2532</v>
+      <c r="Y2" s="245" t="s">
+        <v>2524</v>
       </c>
       <c r="Z2" s="141" t="s">
-        <v>2530</v>
+        <v>2522</v>
       </c>
       <c r="AA2" s="137" t="s">
         <v>1570</v>
@@ -9445,7 +9412,7 @@
         <v>1666</v>
       </c>
       <c r="AO2" s="205" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="AP2" s="184" t="s">
         <v>1652</v>
@@ -9468,7 +9435,7 @@
       <c r="AV2" s="178" t="s">
         <v>1672</v>
       </c>
-      <c r="AW2" s="222">
+      <c r="AW2" s="219">
         <v>99507</v>
       </c>
       <c r="AX2" s="138" t="s">
@@ -9505,7 +9472,7 @@
       <c r="BK2" s="194" t="s">
         <v>1672</v>
       </c>
-      <c r="BL2" s="245">
+      <c r="BL2" s="115">
         <v>99507</v>
       </c>
       <c r="BM2" s="144" t="s">
@@ -9581,12 +9548,12 @@
         <v>2432</v>
       </c>
     </row>
-    <row r="3" spans="1:89" ht="35" thickBot="1">
+    <row r="3" spans="1:89" ht="46.8" thickBot="1">
       <c r="A3" s="135" t="s">
         <v>1677</v>
       </c>
-      <c r="B3" s="214" t="s">
-        <v>2498</v>
+      <c r="B3" s="213" t="s">
+        <v>2490</v>
       </c>
       <c r="C3" s="137" t="s">
         <v>3</v>
@@ -9615,31 +9582,31 @@
       <c r="K3" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="217"/>
-      <c r="R3" s="261"/>
-      <c r="S3" s="258" t="s">
+      <c r="Q3" s="140"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="242" t="s">
         <v>1642</v>
       </c>
-      <c r="T3" s="258" t="s">
+      <c r="T3" s="242" t="s">
         <v>1643</v>
       </c>
-      <c r="U3" s="262" t="s">
+      <c r="U3" s="244" t="s">
         <v>2287</v>
       </c>
       <c r="V3" s="141">
         <v>35750</v>
       </c>
-      <c r="W3" s="259" t="s">
+      <c r="W3" s="243" t="s">
         <v>5</v>
       </c>
       <c r="X3" s="141" t="s">
         <v>2302</v>
       </c>
-      <c r="Y3" s="263" t="s">
-        <v>2532</v>
+      <c r="Y3" s="245" t="s">
+        <v>2524</v>
       </c>
       <c r="Z3" s="141" t="s">
-        <v>2530</v>
+        <v>2522</v>
       </c>
       <c r="AA3" s="137" t="s">
         <v>1570</v>
@@ -9705,7 +9672,7 @@
       <c r="AV3" s="178" t="s">
         <v>1648</v>
       </c>
-      <c r="AW3" s="222">
+      <c r="AW3" s="219">
         <v>35750</v>
       </c>
       <c r="AX3" s="138" t="s">
@@ -9742,7 +9709,7 @@
       <c r="BK3" s="194" t="s">
         <v>1648</v>
       </c>
-      <c r="BL3" s="245">
+      <c r="BL3" s="115">
         <v>85338</v>
       </c>
       <c r="BM3" s="144" t="s">
@@ -9822,14 +9789,14 @@
       <c r="A4" s="155" t="s">
         <v>1693</v>
       </c>
-      <c r="B4" s="209" t="s">
-        <v>2448</v>
+      <c r="B4" s="203" t="s">
+        <v>2526</v>
       </c>
       <c r="C4" s="204" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="156" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="E4" s="152" t="s">
         <v>1641</v>
@@ -9897,7 +9864,7 @@
         <v>1701</v>
       </c>
       <c r="AO4" s="192" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="AP4" s="154" t="s">
         <v>1652</v>
@@ -9920,7 +9887,7 @@
       <c r="AV4" s="152" t="s">
         <v>1706</v>
       </c>
-      <c r="AW4" s="223">
+      <c r="AW4" s="220">
         <v>72034</v>
       </c>
       <c r="AX4" s="157" t="s">
@@ -9957,7 +9924,7 @@
       <c r="BK4" s="152" t="s">
         <v>1706</v>
       </c>
-      <c r="BL4" s="246">
+      <c r="BL4" s="238">
         <v>72034</v>
       </c>
       <c r="BM4" s="161" t="s">
@@ -10033,12 +10000,12 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="5" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="5" spans="1:89" s="152" customFormat="1" ht="46.2" thickBot="1">
       <c r="A5" s="155" t="s">
         <v>1716</v>
       </c>
-      <c r="B5" s="209" t="s">
-        <v>2453</v>
+      <c r="B5" s="203" t="s">
+        <v>2527</v>
       </c>
       <c r="C5" s="152" t="s">
         <v>3</v>
@@ -10080,7 +10047,7 @@
         <v>85253</v>
       </c>
       <c r="P5" s="153" t="s">
-        <v>2533</v>
+        <v>2525</v>
       </c>
       <c r="Q5" s="153" t="s">
         <v>2297</v>
@@ -10114,7 +10081,7 @@
         <v>1724</v>
       </c>
       <c r="AO5" s="192" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="AP5" s="154" t="s">
         <v>1652</v>
@@ -10137,16 +10104,16 @@
       <c r="AV5" s="152" t="s">
         <v>1728</v>
       </c>
-      <c r="AW5" s="224">
+      <c r="AW5" s="221">
         <v>85253</v>
       </c>
       <c r="AX5" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY5" s="211"/>
-      <c r="AZ5" s="211"/>
-      <c r="BA5" s="211"/>
-      <c r="BB5" s="211"/>
+      <c r="AY5" s="191"/>
+      <c r="AZ5" s="191"/>
+      <c r="BA5" s="191"/>
+      <c r="BB5" s="191"/>
       <c r="BC5" s="163" t="s">
         <v>1729</v>
       </c>
@@ -10157,7 +10124,7 @@
         <v>1730</v>
       </c>
       <c r="BF5" s="208" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="BG5" s="166" t="s">
         <v>1731</v>
@@ -10174,7 +10141,7 @@
       <c r="BK5" s="168" t="s">
         <v>1728</v>
       </c>
-      <c r="BL5" s="247">
+      <c r="BL5" s="169">
         <v>85253</v>
       </c>
       <c r="BM5" s="161" t="s">
@@ -10250,12 +10217,12 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="6" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="6" spans="1:89" s="152" customFormat="1" ht="46.2" thickBot="1">
       <c r="A6" s="155" t="s">
         <v>1739</v>
       </c>
       <c r="B6" s="209" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="C6" s="152" t="s">
         <v>3</v>
@@ -10331,7 +10298,7 @@
         <v>1746</v>
       </c>
       <c r="AO6" s="192" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="AP6" s="154" t="s">
         <v>2256</v>
@@ -10354,16 +10321,16 @@
       <c r="AV6" s="152" t="s">
         <v>1750</v>
       </c>
-      <c r="AW6" s="224">
+      <c r="AW6" s="221">
         <v>90805</v>
       </c>
       <c r="AX6" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY6" s="211"/>
-      <c r="AZ6" s="211"/>
-      <c r="BA6" s="211"/>
-      <c r="BB6" s="211"/>
+      <c r="AY6" s="191"/>
+      <c r="AZ6" s="191"/>
+      <c r="BA6" s="191"/>
+      <c r="BB6" s="191"/>
       <c r="BC6" s="163" t="s">
         <v>1751</v>
       </c>
@@ -10391,7 +10358,7 @@
       <c r="BK6" s="152" t="s">
         <v>1750</v>
       </c>
-      <c r="BL6" s="248">
+      <c r="BL6" s="170">
         <v>90805</v>
       </c>
       <c r="BM6" s="161" t="s">
@@ -10467,12 +10434,12 @@
         <v>2324</v>
       </c>
     </row>
-    <row r="7" spans="1:89" s="152" customFormat="1" ht="35" thickBot="1">
+    <row r="7" spans="1:89" s="152" customFormat="1" ht="46.2" thickBot="1">
       <c r="A7" s="155" t="s">
         <v>1761</v>
       </c>
       <c r="B7" s="209" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="C7" s="152" t="s">
         <v>3</v>
@@ -10548,7 +10515,7 @@
         <v>1768</v>
       </c>
       <c r="AO7" s="192" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="AP7" s="154" t="s">
         <v>1652</v>
@@ -10571,16 +10538,16 @@
       <c r="AV7" s="152" t="s">
         <v>1772</v>
       </c>
-      <c r="AW7" s="224">
+      <c r="AW7" s="221">
         <v>80232</v>
       </c>
       <c r="AX7" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY7" s="211"/>
-      <c r="AZ7" s="211"/>
-      <c r="BA7" s="211"/>
-      <c r="BB7" s="211"/>
+      <c r="AY7" s="191"/>
+      <c r="AZ7" s="191"/>
+      <c r="BA7" s="191"/>
+      <c r="BB7" s="191"/>
       <c r="BC7" s="163" t="s">
         <v>1773</v>
       </c>
@@ -10608,7 +10575,7 @@
       <c r="BK7" s="152" t="s">
         <v>1772</v>
       </c>
-      <c r="BL7" s="247">
+      <c r="BL7" s="169">
         <v>33024</v>
       </c>
       <c r="BM7" s="161" t="s">
@@ -10684,12 +10651,12 @@
         <v>2325</v>
       </c>
     </row>
-    <row r="8" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="8" spans="1:89" s="152" customFormat="1" ht="46.2" thickBot="1">
       <c r="A8" s="155" t="s">
         <v>1784</v>
       </c>
       <c r="B8" s="203" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="C8" s="152" t="s">
         <v>3</v>
@@ -10765,7 +10732,7 @@
         <v>1791</v>
       </c>
       <c r="AO8" s="192" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
       <c r="AP8" s="154" t="s">
         <v>1652</v>
@@ -10788,16 +10755,16 @@
       <c r="AV8" s="152" t="s">
         <v>1795</v>
       </c>
-      <c r="AW8" s="224">
+      <c r="AW8" s="221">
         <v>33063</v>
       </c>
       <c r="AX8" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY8" s="211"/>
-      <c r="AZ8" s="211"/>
-      <c r="BA8" s="211"/>
-      <c r="BB8" s="211"/>
+      <c r="AY8" s="191"/>
+      <c r="AZ8" s="191"/>
+      <c r="BA8" s="191"/>
+      <c r="BB8" s="191"/>
       <c r="BC8" s="163" t="s">
         <v>1796</v>
       </c>
@@ -10825,7 +10792,7 @@
       <c r="BK8" s="168" t="s">
         <v>2295</v>
       </c>
-      <c r="BL8" s="248">
+      <c r="BL8" s="170">
         <v>33063</v>
       </c>
       <c r="BM8" s="161" t="s">
@@ -10901,12 +10868,12 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="9" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="9" spans="1:89" s="152" customFormat="1" ht="46.2" thickBot="1">
       <c r="A9" s="155" t="s">
         <v>1807</v>
       </c>
       <c r="B9" s="209" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="C9" s="152" t="s">
         <v>3</v>
@@ -10982,7 +10949,7 @@
         <v>1814</v>
       </c>
       <c r="AO9" s="192" t="s">
-        <v>2462</v>
+        <v>2459</v>
       </c>
       <c r="AP9" s="154" t="s">
         <v>1667</v>
@@ -11005,16 +10972,16 @@
       <c r="AV9" s="152" t="s">
         <v>2291</v>
       </c>
-      <c r="AW9" s="224">
+      <c r="AW9" s="221">
         <v>30114</v>
       </c>
       <c r="AX9" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY9" s="211"/>
-      <c r="AZ9" s="211"/>
-      <c r="BA9" s="211"/>
-      <c r="BB9" s="211"/>
+      <c r="AY9" s="191"/>
+      <c r="AZ9" s="191"/>
+      <c r="BA9" s="191"/>
+      <c r="BB9" s="191"/>
       <c r="BC9" s="163" t="s">
         <v>1818</v>
       </c>
@@ -11025,7 +10992,7 @@
         <v>1819</v>
       </c>
       <c r="BF9" s="206" t="s">
-        <v>2502</v>
+        <v>2494</v>
       </c>
       <c r="BG9" s="166" t="s">
         <v>1821</v>
@@ -11034,15 +11001,15 @@
         <v>2392</v>
       </c>
       <c r="BI9" s="154" t="s">
-        <v>2516</v>
+        <v>2508</v>
       </c>
       <c r="BJ9" s="167" t="s">
         <v>2296</v>
       </c>
-      <c r="BK9" s="215" t="s">
-        <v>2517</v>
-      </c>
-      <c r="BL9" s="249">
+      <c r="BK9" s="214" t="s">
+        <v>2509</v>
+      </c>
+      <c r="BL9" s="154">
         <v>33418</v>
       </c>
       <c r="BM9" s="161" t="s">
@@ -11118,12 +11085,12 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="10" spans="1:89" ht="53" thickBot="1">
+    <row r="10" spans="1:89" ht="47.4" thickBot="1">
       <c r="A10" s="135" t="s">
         <v>1829</v>
       </c>
-      <c r="B10" s="214" t="s">
-        <v>2499</v>
+      <c r="B10" s="213" t="s">
+        <v>2491</v>
       </c>
       <c r="C10" s="137" t="s">
         <v>3</v>
@@ -11224,7 +11191,7 @@
         <v>1836</v>
       </c>
       <c r="AO10" s="192" t="s">
-        <v>2520</v>
+        <v>2512</v>
       </c>
       <c r="AP10" s="184" t="s">
         <v>1652</v>
@@ -11247,7 +11214,7 @@
       <c r="AV10" s="198" t="s">
         <v>2444</v>
       </c>
-      <c r="AW10" s="222">
+      <c r="AW10" s="219">
         <v>96706</v>
       </c>
       <c r="AX10" s="138" t="s">
@@ -11267,7 +11234,7 @@
         <v>1842</v>
       </c>
       <c r="BF10" s="206" t="s">
-        <v>2503</v>
+        <v>2495</v>
       </c>
       <c r="BG10" s="150" t="s">
         <v>1843</v>
@@ -11284,7 +11251,7 @@
       <c r="BK10" s="194" t="s">
         <v>2413</v>
       </c>
-      <c r="BL10" s="250">
+      <c r="BL10" s="122">
         <v>33805</v>
       </c>
       <c r="BM10" s="144" t="s">
@@ -11302,10 +11269,10 @@
       <c r="BQ10" s="138" t="s">
         <v>1583</v>
       </c>
-      <c r="BR10" s="217" t="s">
+      <c r="BR10" s="140" t="s">
         <v>1687</v>
       </c>
-      <c r="BS10" s="218" t="s">
+      <c r="BS10" s="142" t="s">
         <v>1545</v>
       </c>
       <c r="BT10" s="140" t="s">
@@ -11360,12 +11327,12 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="11" spans="1:89" s="152" customFormat="1" ht="35" thickBot="1">
+    <row r="11" spans="1:89" s="152" customFormat="1" ht="46.2" thickBot="1">
       <c r="A11" s="155" t="s">
         <v>1850</v>
       </c>
-      <c r="B11" s="213" t="s">
-        <v>2500</v>
+      <c r="B11" s="212" t="s">
+        <v>2492</v>
       </c>
       <c r="C11" s="152" t="s">
         <v>3</v>
@@ -11466,7 +11433,7 @@
         <v>1857</v>
       </c>
       <c r="AO11" s="192" t="s">
-        <v>2468</v>
+        <v>2465</v>
       </c>
       <c r="AP11" s="154" t="s">
         <v>1652</v>
@@ -11489,16 +11456,16 @@
       <c r="AV11" s="152" t="s">
         <v>1861</v>
       </c>
-      <c r="AW11" s="224">
+      <c r="AW11" s="221">
         <v>83605</v>
       </c>
       <c r="AX11" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY11" s="211"/>
-      <c r="AZ11" s="211"/>
-      <c r="BA11" s="211"/>
-      <c r="BB11" s="211"/>
+      <c r="AY11" s="191"/>
+      <c r="AZ11" s="191"/>
+      <c r="BA11" s="191"/>
+      <c r="BB11" s="191"/>
       <c r="BC11" s="163" t="s">
         <v>1862</v>
       </c>
@@ -11508,8 +11475,8 @@
       <c r="BE11" s="163" t="s">
         <v>1863</v>
       </c>
-      <c r="BF11" s="219" t="s">
-        <v>2504</v>
+      <c r="BF11" s="216" t="s">
+        <v>2496</v>
       </c>
       <c r="BG11" s="166" t="s">
         <v>1864</v>
@@ -11526,7 +11493,7 @@
       <c r="BK11" s="152" t="s">
         <v>2414</v>
       </c>
-      <c r="BL11" s="251">
+      <c r="BL11" s="120">
         <v>83605</v>
       </c>
       <c r="BM11" s="161" t="s">
@@ -11595,19 +11562,19 @@
       <c r="CI11" s="153" t="s">
         <v>1660</v>
       </c>
-      <c r="CJ11" s="220" t="s">
+      <c r="CJ11" s="217" t="s">
         <v>2226</v>
       </c>
       <c r="CK11" s="164" t="s">
         <v>2319</v>
       </c>
     </row>
-    <row r="12" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="12" spans="1:89" s="152" customFormat="1" ht="46.2" thickBot="1">
       <c r="A12" s="155" t="s">
         <v>1872</v>
       </c>
-      <c r="B12" s="213" t="s">
-        <v>2501</v>
+      <c r="B12" s="212" t="s">
+        <v>2493</v>
       </c>
       <c r="C12" s="152" t="s">
         <v>3</v>
@@ -11708,7 +11675,7 @@
         <v>1878</v>
       </c>
       <c r="AO12" s="192" t="s">
-        <v>2469</v>
+        <v>2466</v>
       </c>
       <c r="AP12" s="154" t="s">
         <v>1667</v>
@@ -11731,16 +11698,16 @@
       <c r="AV12" s="152" t="s">
         <v>1882</v>
       </c>
-      <c r="AW12" s="224">
+      <c r="AW12" s="221">
         <v>60632</v>
       </c>
       <c r="AX12" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY12" s="211"/>
-      <c r="AZ12" s="211"/>
-      <c r="BA12" s="211"/>
-      <c r="BB12" s="211"/>
+      <c r="AY12" s="191"/>
+      <c r="AZ12" s="191"/>
+      <c r="BA12" s="191"/>
+      <c r="BB12" s="191"/>
       <c r="BC12" s="163" t="s">
         <v>1883</v>
       </c>
@@ -11750,7 +11717,7 @@
       <c r="BE12" s="163" t="s">
         <v>1884</v>
       </c>
-      <c r="BF12" s="219" t="s">
+      <c r="BF12" s="216" t="s">
         <v>1885</v>
       </c>
       <c r="BG12" s="166" t="s">
@@ -11768,7 +11735,7 @@
       <c r="BK12" s="152" t="s">
         <v>1882</v>
       </c>
-      <c r="BL12" s="251">
+      <c r="BL12" s="120">
         <v>60632</v>
       </c>
       <c r="BM12" s="161" t="s">
@@ -11837,235 +11804,235 @@
       <c r="CI12" s="153" t="s">
         <v>1660</v>
       </c>
-      <c r="CJ12" s="220" t="s">
+      <c r="CJ12" s="217" t="s">
         <v>2226</v>
       </c>
       <c r="CK12" s="164" t="s">
         <v>2319</v>
       </c>
     </row>
-    <row r="13" spans="1:89" s="227" customFormat="1" ht="52" thickBot="1">
-      <c r="A13" s="227" t="s">
+    <row r="13" spans="1:89" s="224" customFormat="1" ht="61.2" thickBot="1">
+      <c r="A13" s="224" t="s">
         <v>1893</v>
       </c>
-      <c r="B13" s="228" t="s">
-        <v>2460</v>
-      </c>
-      <c r="C13" s="227" t="s">
+      <c r="B13" s="209" t="s">
+        <v>2533</v>
+      </c>
+      <c r="C13" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="229" t="s">
+      <c r="D13" s="225" t="s">
         <v>2237</v>
       </c>
-      <c r="E13" s="227" t="s">
+      <c r="E13" s="224" t="s">
         <v>1641</v>
       </c>
-      <c r="F13" s="230" t="s">
+      <c r="F13" s="226" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="227" t="s">
+      <c r="G13" s="224" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="231" t="s">
+      <c r="H13" s="227" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="231" t="s">
+      <c r="I13" s="227" t="s">
         <v>13</v>
       </c>
-      <c r="J13" s="231" t="s">
+      <c r="J13" s="227" t="s">
         <v>14</v>
       </c>
-      <c r="K13" s="230" t="s">
+      <c r="K13" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="227" t="s">
+      <c r="L13" s="224" t="s">
         <v>1903</v>
       </c>
-      <c r="M13" s="227" t="s">
+      <c r="M13" s="224" t="s">
         <v>1904</v>
       </c>
-      <c r="N13" s="227" t="s">
+      <c r="N13" s="224" t="s">
         <v>2305</v>
       </c>
-      <c r="O13" s="232">
+      <c r="O13" s="220">
         <v>47521</v>
       </c>
-      <c r="P13" s="232" t="s">
+      <c r="P13" s="220" t="s">
         <v>2302</v>
       </c>
-      <c r="Q13" s="232" t="s">
+      <c r="Q13" s="220" t="s">
         <v>2303</v>
       </c>
-      <c r="R13" s="232" t="s">
+      <c r="R13" s="220" t="s">
         <v>2304</v>
       </c>
-      <c r="S13" s="232"/>
-      <c r="T13" s="232"/>
-      <c r="U13" s="232"/>
-      <c r="V13" s="232"/>
-      <c r="W13" s="232"/>
-      <c r="X13" s="232"/>
-      <c r="Y13" s="232"/>
-      <c r="Z13" s="232"/>
-      <c r="AC13" s="230"/>
-      <c r="AD13" s="233"/>
-      <c r="AE13" s="233"/>
-      <c r="AF13" s="233"/>
-      <c r="AG13" s="233"/>
-      <c r="AJ13" s="230"/>
-      <c r="AK13" s="233"/>
-      <c r="AL13" s="234" t="s">
+      <c r="S13" s="220"/>
+      <c r="T13" s="220"/>
+      <c r="U13" s="220"/>
+      <c r="V13" s="220"/>
+      <c r="W13" s="220"/>
+      <c r="X13" s="220"/>
+      <c r="Y13" s="220"/>
+      <c r="Z13" s="220"/>
+      <c r="AC13" s="226"/>
+      <c r="AD13" s="228"/>
+      <c r="AE13" s="228"/>
+      <c r="AF13" s="228"/>
+      <c r="AG13" s="228"/>
+      <c r="AJ13" s="226"/>
+      <c r="AK13" s="228"/>
+      <c r="AL13" s="221" t="s">
         <v>1899</v>
       </c>
-      <c r="AM13" s="235" t="s">
+      <c r="AM13" s="229" t="s">
         <v>2257</v>
       </c>
-      <c r="AN13" s="234" t="s">
+      <c r="AN13" s="221" t="s">
         <v>1900</v>
       </c>
-      <c r="AO13" s="236" t="s">
-        <v>2470</v>
-      </c>
-      <c r="AP13" s="235" t="s">
+      <c r="AO13" s="230" t="s">
+        <v>2467</v>
+      </c>
+      <c r="AP13" s="229" t="s">
         <v>1667</v>
       </c>
-      <c r="AQ13" s="237" t="s">
+      <c r="AQ13" s="231" t="s">
         <v>2364</v>
       </c>
-      <c r="AR13" s="238" t="s">
+      <c r="AR13" s="232" t="s">
         <v>1902</v>
       </c>
-      <c r="AS13" s="233" t="s">
+      <c r="AS13" s="228" t="s">
         <v>1688</v>
       </c>
-      <c r="AT13" s="234" t="s">
+      <c r="AT13" s="221" t="s">
         <v>1903</v>
       </c>
-      <c r="AU13" s="231" t="s">
+      <c r="AU13" s="227" t="s">
         <v>2306</v>
       </c>
-      <c r="AV13" s="227" t="s">
+      <c r="AV13" s="224" t="s">
         <v>1904</v>
       </c>
-      <c r="AW13" s="224">
+      <c r="AW13" s="221">
         <v>47521</v>
       </c>
-      <c r="AX13" s="230" t="s">
+      <c r="AX13" s="226" t="s">
         <v>1597</v>
       </c>
-      <c r="AY13" s="239"/>
-      <c r="AZ13" s="239"/>
-      <c r="BA13" s="239"/>
-      <c r="BB13" s="239"/>
-      <c r="BC13" s="238" t="s">
+      <c r="AY13" s="230"/>
+      <c r="AZ13" s="230"/>
+      <c r="BA13" s="230"/>
+      <c r="BB13" s="230"/>
+      <c r="BC13" s="232" t="s">
         <v>1905</v>
       </c>
-      <c r="BD13" s="240" t="s">
+      <c r="BD13" s="233" t="s">
         <v>2267</v>
       </c>
-      <c r="BE13" s="238" t="s">
+      <c r="BE13" s="232" t="s">
         <v>1906</v>
       </c>
-      <c r="BF13" s="241" t="s">
+      <c r="BF13" s="234" t="s">
         <v>1907</v>
       </c>
-      <c r="BG13" s="242" t="s">
+      <c r="BG13" s="235" t="s">
         <v>1908</v>
       </c>
-      <c r="BH13" s="235" t="s">
+      <c r="BH13" s="229" t="s">
         <v>2312</v>
       </c>
-      <c r="BI13" s="235" t="s">
+      <c r="BI13" s="229" t="s">
         <v>1903</v>
       </c>
-      <c r="BJ13" s="243" t="s">
+      <c r="BJ13" s="236" t="s">
         <v>2315</v>
       </c>
-      <c r="BK13" s="227" t="s">
+      <c r="BK13" s="224" t="s">
         <v>1904</v>
       </c>
-      <c r="BL13" s="252">
+      <c r="BL13" s="233">
         <v>47521</v>
       </c>
-      <c r="BM13" s="230" t="s">
+      <c r="BM13" s="226" t="s">
         <v>1597</v>
       </c>
-      <c r="BN13" s="227" t="s">
+      <c r="BN13" s="224" t="s">
         <v>1537</v>
       </c>
-      <c r="BO13" s="227" t="s">
+      <c r="BO13" s="224" t="s">
         <v>1537</v>
       </c>
-      <c r="BP13" s="227" t="s">
+      <c r="BP13" s="224" t="s">
         <v>1543</v>
       </c>
-      <c r="BQ13" s="230" t="s">
+      <c r="BQ13" s="226" t="s">
         <v>1583</v>
       </c>
-      <c r="BR13" s="232" t="s">
+      <c r="BR13" s="220" t="s">
         <v>1687</v>
       </c>
-      <c r="BS13" s="233" t="s">
+      <c r="BS13" s="228" t="s">
         <v>1545</v>
       </c>
-      <c r="BT13" s="232" t="s">
+      <c r="BT13" s="220" t="s">
         <v>1547</v>
       </c>
-      <c r="BU13" s="232" t="s">
+      <c r="BU13" s="220" t="s">
         <v>1551</v>
       </c>
-      <c r="BV13" s="232" t="s">
+      <c r="BV13" s="220" t="s">
         <v>1552</v>
       </c>
-      <c r="BW13" s="232" t="s">
+      <c r="BW13" s="220" t="s">
         <v>1523</v>
       </c>
-      <c r="BX13" s="232" t="s">
+      <c r="BX13" s="220" t="s">
         <v>1554</v>
       </c>
-      <c r="BY13" s="227" t="s">
+      <c r="BY13" s="224" t="s">
         <v>1556</v>
       </c>
-      <c r="BZ13" s="232" t="s">
+      <c r="BZ13" s="220" t="s">
         <v>1558</v>
       </c>
-      <c r="CA13" s="232" t="s">
+      <c r="CA13" s="220" t="s">
         <v>1565</v>
       </c>
-      <c r="CB13" s="232" t="s">
+      <c r="CB13" s="220" t="s">
         <v>1566</v>
       </c>
-      <c r="CC13" s="232" t="s">
+      <c r="CC13" s="220" t="s">
         <v>1567</v>
       </c>
-      <c r="CD13" s="232" t="s">
+      <c r="CD13" s="220" t="s">
         <v>1568</v>
       </c>
-      <c r="CF13" s="227" t="s">
+      <c r="CF13" s="224" t="s">
         <v>1629</v>
       </c>
-      <c r="CG13" s="227" t="s">
+      <c r="CG13" s="224" t="s">
         <v>1630</v>
       </c>
-      <c r="CH13" s="232" t="s">
+      <c r="CH13" s="220" t="s">
         <v>2303</v>
       </c>
-      <c r="CI13" s="232" t="s">
+      <c r="CI13" s="220" t="s">
         <v>1660</v>
       </c>
-      <c r="CJ13" s="244" t="s">
+      <c r="CJ13" s="237" t="s">
         <v>2226</v>
       </c>
-      <c r="CK13" s="234" t="s">
+      <c r="CK13" s="221" t="s">
         <v>2319</v>
       </c>
     </row>
-    <row r="14" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="14" spans="1:89" s="152" customFormat="1" ht="46.2" thickBot="1">
       <c r="A14" s="155" t="s">
         <v>1915</v>
       </c>
       <c r="B14" s="209" t="s">
-        <v>2461</v>
+        <v>2458</v>
       </c>
       <c r="C14" s="152" t="s">
         <v>3</v>
@@ -12141,7 +12108,7 @@
         <v>1922</v>
       </c>
       <c r="AO14" s="191" t="s">
-        <v>2463</v>
+        <v>2460</v>
       </c>
       <c r="AP14" s="154" t="s">
         <v>1652</v>
@@ -12164,16 +12131,16 @@
       <c r="AV14" s="152" t="s">
         <v>1926</v>
       </c>
-      <c r="AW14" s="224">
+      <c r="AW14" s="221">
         <v>70726</v>
       </c>
       <c r="AX14" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY14" s="211"/>
-      <c r="AZ14" s="211"/>
-      <c r="BA14" s="211"/>
-      <c r="BB14" s="211"/>
+      <c r="AY14" s="191"/>
+      <c r="AZ14" s="191"/>
+      <c r="BA14" s="191"/>
+      <c r="BB14" s="191"/>
       <c r="BC14" s="163" t="s">
         <v>1927</v>
       </c>
@@ -12184,7 +12151,7 @@
         <v>1928</v>
       </c>
       <c r="BF14" s="208" t="s">
-        <v>2505</v>
+        <v>2497</v>
       </c>
       <c r="BG14" s="166" t="s">
         <v>1929</v>
@@ -12201,7 +12168,7 @@
       <c r="BK14" s="168" t="s">
         <v>2317</v>
       </c>
-      <c r="BL14" s="251">
+      <c r="BL14" s="120">
         <v>71303</v>
       </c>
       <c r="BM14" s="161" t="s">
@@ -12277,12 +12244,12 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="15" spans="1:89" ht="52" thickBot="1">
+    <row r="15" spans="1:89" ht="46.8" thickBot="1">
       <c r="A15" s="135" t="s">
         <v>1936</v>
       </c>
-      <c r="B15" s="214" t="s">
-        <v>2493</v>
+      <c r="B15" s="213" t="s">
+        <v>2485</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>3</v>
@@ -12383,7 +12350,7 @@
         <v>1943</v>
       </c>
       <c r="AO15" s="191" t="s">
-        <v>2471</v>
+        <v>2468</v>
       </c>
       <c r="AP15" s="184" t="s">
         <v>1652</v>
@@ -12406,7 +12373,7 @@
       <c r="AV15" s="176" t="s">
         <v>1948</v>
       </c>
-      <c r="AW15" s="222">
+      <c r="AW15" s="219">
         <v>21060</v>
       </c>
       <c r="AX15" s="138" t="s">
@@ -12426,7 +12393,7 @@
         <v>1950</v>
       </c>
       <c r="BF15" s="208" t="s">
-        <v>2506</v>
+        <v>2498</v>
       </c>
       <c r="BG15" s="150" t="s">
         <v>1951</v>
@@ -12443,7 +12410,7 @@
       <c r="BK15" s="194" t="s">
         <v>1948</v>
       </c>
-      <c r="BL15" s="253">
+      <c r="BL15" s="189">
         <v>21060</v>
       </c>
       <c r="BM15" s="144" t="s">
@@ -12461,10 +12428,10 @@
       <c r="BQ15" s="138" t="s">
         <v>1583</v>
       </c>
-      <c r="BR15" s="217" t="s">
+      <c r="BR15" s="140" t="s">
         <v>1687</v>
       </c>
-      <c r="BS15" s="218" t="s">
+      <c r="BS15" s="142" t="s">
         <v>1545</v>
       </c>
       <c r="BT15" s="140" t="s">
@@ -12519,12 +12486,12 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="16" spans="1:89" ht="52" thickBot="1">
+    <row r="16" spans="1:89" ht="46.2" thickBot="1">
       <c r="A16" s="135" t="s">
         <v>1958</v>
       </c>
-      <c r="B16" s="214" t="s">
-        <v>2494</v>
+      <c r="B16" s="213" t="s">
+        <v>2486</v>
       </c>
       <c r="C16" s="137" t="s">
         <v>3</v>
@@ -12625,7 +12592,7 @@
         <v>1964</v>
       </c>
       <c r="AO16" s="191" t="s">
-        <v>2472</v>
+        <v>2469</v>
       </c>
       <c r="AP16" s="184" t="s">
         <v>1667</v>
@@ -12648,7 +12615,7 @@
       <c r="AV16" s="176" t="s">
         <v>1968</v>
       </c>
-      <c r="AW16" s="222">
+      <c r="AW16" s="219">
         <v>49315</v>
       </c>
       <c r="AX16" s="138" t="s">
@@ -12685,7 +12652,7 @@
       <c r="BK16" s="195" t="s">
         <v>1968</v>
       </c>
-      <c r="BL16" s="250">
+      <c r="BL16" s="122">
         <v>49315</v>
       </c>
       <c r="BM16" s="144" t="s">
@@ -12703,10 +12670,10 @@
       <c r="BQ16" s="138" t="s">
         <v>1583</v>
       </c>
-      <c r="BR16" s="217" t="s">
+      <c r="BR16" s="140" t="s">
         <v>1687</v>
       </c>
-      <c r="BS16" s="218" t="s">
+      <c r="BS16" s="142" t="s">
         <v>1545</v>
       </c>
       <c r="BT16" s="140" t="s">
@@ -12761,12 +12728,12 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="17" spans="1:89" ht="35" thickBot="1">
+    <row r="17" spans="1:89" ht="31.2" thickBot="1">
       <c r="A17" s="135" t="s">
         <v>1979</v>
       </c>
-      <c r="B17" s="214" t="s">
-        <v>2495</v>
+      <c r="B17" s="213" t="s">
+        <v>2487</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>3</v>
@@ -12867,7 +12834,7 @@
         <v>1986</v>
       </c>
       <c r="AO17" s="191" t="s">
-        <v>2519</v>
+        <v>2511</v>
       </c>
       <c r="AP17" s="184" t="s">
         <v>1652</v>
@@ -12890,7 +12857,7 @@
       <c r="AV17" s="176" t="s">
         <v>1990</v>
       </c>
-      <c r="AW17" s="222">
+      <c r="AW17" s="219">
         <v>59715</v>
       </c>
       <c r="AX17" s="138" t="s">
@@ -12910,7 +12877,7 @@
         <v>1991</v>
       </c>
       <c r="BF17" s="208" t="s">
-        <v>2507</v>
+        <v>2499</v>
       </c>
       <c r="BG17" s="149" t="s">
         <v>1993</v>
@@ -12927,7 +12894,7 @@
       <c r="BK17" s="195" t="s">
         <v>2419</v>
       </c>
-      <c r="BL17" s="250">
+      <c r="BL17" s="122">
         <v>64118</v>
       </c>
       <c r="BM17" s="144" t="s">
@@ -12945,10 +12912,10 @@
       <c r="BQ17" s="138" t="s">
         <v>1583</v>
       </c>
-      <c r="BR17" s="217" t="s">
+      <c r="BR17" s="140" t="s">
         <v>1687</v>
       </c>
-      <c r="BS17" s="218" t="s">
+      <c r="BS17" s="142" t="s">
         <v>1545</v>
       </c>
       <c r="BT17" s="140" t="s">
@@ -13003,12 +12970,12 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="18" spans="1:89" ht="35" thickBot="1">
+    <row r="18" spans="1:89" ht="46.8" thickBot="1">
       <c r="A18" s="135" t="s">
         <v>2000</v>
       </c>
-      <c r="B18" s="216" t="s">
-        <v>2496</v>
+      <c r="B18" s="215" t="s">
+        <v>2488</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>3</v>
@@ -13109,7 +13076,7 @@
         <v>2006</v>
       </c>
       <c r="AO18" s="191" t="s">
-        <v>2464</v>
+        <v>2461</v>
       </c>
       <c r="AP18" s="184" t="s">
         <v>1652</v>
@@ -13132,7 +13099,7 @@
       <c r="AV18" s="176" t="s">
         <v>2010</v>
       </c>
-      <c r="AW18" s="222">
+      <c r="AW18" s="219">
         <v>64118</v>
       </c>
       <c r="AX18" s="138" t="s">
@@ -13152,7 +13119,7 @@
         <v>2012</v>
       </c>
       <c r="BF18" s="208" t="s">
-        <v>2508</v>
+        <v>2500</v>
       </c>
       <c r="BG18" s="150" t="s">
         <v>2014</v>
@@ -13169,7 +13136,7 @@
       <c r="BK18" s="194" t="s">
         <v>2010</v>
       </c>
-      <c r="BL18" s="250">
+      <c r="BL18" s="122">
         <v>59715</v>
       </c>
       <c r="BM18" s="144" t="s">
@@ -13187,10 +13154,10 @@
       <c r="BQ18" s="138" t="s">
         <v>1583</v>
       </c>
-      <c r="BR18" s="217" t="s">
+      <c r="BR18" s="140" t="s">
         <v>1687</v>
       </c>
-      <c r="BS18" s="218" t="s">
+      <c r="BS18" s="142" t="s">
         <v>1545</v>
       </c>
       <c r="BT18" s="140" t="s">
@@ -13245,12 +13212,12 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="19" spans="1:89" s="152" customFormat="1" ht="35" thickBot="1">
+    <row r="19" spans="1:89" s="152" customFormat="1" ht="46.8" thickBot="1">
       <c r="A19" s="155" t="s">
         <v>2022</v>
       </c>
-      <c r="B19" s="213" t="s">
-        <v>2483</v>
+      <c r="B19" s="212" t="s">
+        <v>2480</v>
       </c>
       <c r="C19" s="152" t="s">
         <v>3</v>
@@ -13326,7 +13293,7 @@
         <v>2029</v>
       </c>
       <c r="AO19" s="191" t="s">
-        <v>2521</v>
+        <v>2513</v>
       </c>
       <c r="AP19" s="154" t="s">
         <v>1667</v>
@@ -13349,16 +13316,16 @@
       <c r="AV19" s="152" t="s">
         <v>2034</v>
       </c>
-      <c r="AW19" s="224">
+      <c r="AW19" s="221">
         <v>27525</v>
       </c>
       <c r="AX19" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY19" s="211"/>
-      <c r="AZ19" s="211"/>
-      <c r="BA19" s="211"/>
-      <c r="BB19" s="211"/>
+      <c r="AY19" s="191"/>
+      <c r="AZ19" s="191"/>
+      <c r="BA19" s="191"/>
+      <c r="BB19" s="191"/>
       <c r="BC19" s="154" t="s">
         <v>2035</v>
       </c>
@@ -13369,7 +13336,7 @@
         <v>2036</v>
       </c>
       <c r="BF19" s="208" t="s">
-        <v>2522</v>
+        <v>2514</v>
       </c>
       <c r="BG19" s="166" t="s">
         <v>2037</v>
@@ -13386,7 +13353,7 @@
       <c r="BK19" s="121" t="s">
         <v>2034</v>
       </c>
-      <c r="BL19" s="251">
+      <c r="BL19" s="120">
         <v>27525</v>
       </c>
       <c r="BM19" s="161" t="s">
@@ -13462,12 +13429,12 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="20" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="20" spans="1:89" s="152" customFormat="1" ht="46.8" thickBot="1">
       <c r="A20" s="155" t="s">
         <v>2044</v>
       </c>
-      <c r="B20" s="213" t="s">
-        <v>2484</v>
+      <c r="B20" s="212" t="s">
+        <v>2532</v>
       </c>
       <c r="C20" s="152" t="s">
         <v>3</v>
@@ -13543,7 +13510,7 @@
         <v>2051</v>
       </c>
       <c r="AO20" s="191" t="s">
-        <v>2473</v>
+        <v>2470</v>
       </c>
       <c r="AP20" s="154" t="s">
         <v>1652</v>
@@ -13566,16 +13533,16 @@
       <c r="AV20" s="152" t="s">
         <v>2056</v>
       </c>
-      <c r="AW20" s="224">
+      <c r="AW20" s="221">
         <v>87121</v>
       </c>
       <c r="AX20" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY20" s="211"/>
-      <c r="AZ20" s="211"/>
-      <c r="BA20" s="211"/>
-      <c r="BB20" s="211"/>
+      <c r="AY20" s="191"/>
+      <c r="AZ20" s="191"/>
+      <c r="BA20" s="191"/>
+      <c r="BB20" s="191"/>
       <c r="BC20" s="154" t="s">
         <v>2057</v>
       </c>
@@ -13586,7 +13553,7 @@
         <v>2058</v>
       </c>
       <c r="BF20" s="208" t="s">
-        <v>2509</v>
+        <v>2501</v>
       </c>
       <c r="BG20" s="166" t="s">
         <v>2060</v>
@@ -13603,7 +13570,7 @@
       <c r="BK20" s="121" t="s">
         <v>2056</v>
       </c>
-      <c r="BL20" s="251">
+      <c r="BL20" s="120">
         <v>87121</v>
       </c>
       <c r="BM20" s="161" t="s">
@@ -13679,228 +13646,228 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="21" spans="1:89" s="227" customFormat="1" ht="52" thickBot="1">
-      <c r="A21" s="227" t="s">
+    <row r="21" spans="1:89" s="224" customFormat="1" ht="46.2" thickBot="1">
+      <c r="A21" s="224" t="s">
         <v>2068</v>
       </c>
-      <c r="B21" s="254" t="s">
-        <v>2485</v>
-      </c>
-      <c r="C21" s="227" t="s">
+      <c r="B21" s="212" t="s">
+        <v>2531</v>
+      </c>
+      <c r="C21" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="229" t="s">
+      <c r="D21" s="225" t="s">
         <v>2245</v>
       </c>
-      <c r="E21" s="227" t="s">
+      <c r="E21" s="224" t="s">
         <v>1641</v>
       </c>
-      <c r="F21" s="230" t="s">
+      <c r="F21" s="226" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="227" t="s">
+      <c r="G21" s="224" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="231" t="s">
+      <c r="H21" s="227" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="231" t="s">
+      <c r="I21" s="227" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="231" t="s">
+      <c r="J21" s="227" t="s">
         <v>14</v>
       </c>
-      <c r="K21" s="230" t="s">
+      <c r="K21" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="L21" s="235" t="s">
+      <c r="L21" s="229" t="s">
         <v>2078</v>
       </c>
-      <c r="M21" s="235" t="s">
+      <c r="M21" s="229" t="s">
         <v>2080</v>
       </c>
-      <c r="N21" s="227" t="s">
+      <c r="N21" s="224" t="s">
         <v>2079</v>
       </c>
-      <c r="O21" s="235">
+      <c r="O21" s="229">
         <v>89179</v>
       </c>
-      <c r="P21" s="232" t="s">
+      <c r="P21" s="220" t="s">
         <v>1575</v>
       </c>
-      <c r="Q21" s="232" t="s">
+      <c r="Q21" s="220" t="s">
         <v>1586</v>
       </c>
-      <c r="R21" s="232" t="s">
+      <c r="R21" s="220" t="s">
         <v>1587</v>
       </c>
-      <c r="S21" s="232"/>
-      <c r="T21" s="232"/>
-      <c r="U21" s="232"/>
-      <c r="V21" s="232"/>
-      <c r="W21" s="232"/>
-      <c r="X21" s="232"/>
-      <c r="Y21" s="232"/>
-      <c r="Z21" s="232"/>
-      <c r="AC21" s="230"/>
-      <c r="AD21" s="233"/>
-      <c r="AE21" s="233"/>
-      <c r="AF21" s="233"/>
-      <c r="AG21" s="233"/>
-      <c r="AJ21" s="230"/>
-      <c r="AK21" s="233"/>
-      <c r="AL21" s="235" t="s">
+      <c r="S21" s="220"/>
+      <c r="T21" s="220"/>
+      <c r="U21" s="220"/>
+      <c r="V21" s="220"/>
+      <c r="W21" s="220"/>
+      <c r="X21" s="220"/>
+      <c r="Y21" s="220"/>
+      <c r="Z21" s="220"/>
+      <c r="AC21" s="226"/>
+      <c r="AD21" s="228"/>
+      <c r="AE21" s="228"/>
+      <c r="AF21" s="228"/>
+      <c r="AG21" s="228"/>
+      <c r="AJ21" s="226"/>
+      <c r="AK21" s="228"/>
+      <c r="AL21" s="229" t="s">
         <v>2074</v>
       </c>
-      <c r="AM21" s="235" t="s">
+      <c r="AM21" s="229" t="s">
         <v>2260</v>
       </c>
-      <c r="AN21" s="235" t="s">
+      <c r="AN21" s="229" t="s">
         <v>2075</v>
       </c>
-      <c r="AO21" s="236" t="s">
-        <v>2474</v>
-      </c>
-      <c r="AP21" s="235" t="s">
+      <c r="AO21" s="230" t="s">
+        <v>2471</v>
+      </c>
+      <c r="AP21" s="229" t="s">
         <v>1652</v>
       </c>
-      <c r="AQ21" s="237" t="s">
+      <c r="AQ21" s="231" t="s">
         <v>2372</v>
       </c>
-      <c r="AR21" s="238" t="s">
+      <c r="AR21" s="232" t="s">
         <v>2077</v>
       </c>
-      <c r="AS21" s="233" t="s">
+      <c r="AS21" s="228" t="s">
         <v>1688</v>
       </c>
-      <c r="AT21" s="234" t="s">
-        <v>2523</v>
-      </c>
-      <c r="AU21" s="231" t="s">
+      <c r="AT21" s="221" t="s">
+        <v>2515</v>
+      </c>
+      <c r="AU21" s="227" t="s">
         <v>2424</v>
       </c>
-      <c r="AV21" s="227" t="s">
+      <c r="AV21" s="224" t="s">
         <v>2080</v>
       </c>
-      <c r="AW21" s="224">
+      <c r="AW21" s="221">
         <v>89179</v>
       </c>
-      <c r="AX21" s="230" t="s">
+      <c r="AX21" s="226" t="s">
         <v>1597</v>
       </c>
-      <c r="AY21" s="239"/>
-      <c r="AZ21" s="239"/>
-      <c r="BA21" s="239"/>
-      <c r="BB21" s="239"/>
-      <c r="BC21" s="235" t="s">
+      <c r="AY21" s="230"/>
+      <c r="AZ21" s="230"/>
+      <c r="BA21" s="230"/>
+      <c r="BB21" s="230"/>
+      <c r="BC21" s="229" t="s">
         <v>2081</v>
       </c>
-      <c r="BD21" s="240" t="s">
+      <c r="BD21" s="233" t="s">
         <v>2260</v>
       </c>
-      <c r="BE21" s="235" t="s">
+      <c r="BE21" s="229" t="s">
         <v>2075</v>
       </c>
-      <c r="BF21" s="255" t="s">
+      <c r="BF21" s="239" t="s">
         <v>2082</v>
       </c>
-      <c r="BG21" s="242" t="s">
+      <c r="BG21" s="235" t="s">
         <v>2083</v>
       </c>
-      <c r="BH21" s="235" t="s">
+      <c r="BH21" s="229" t="s">
         <v>2402</v>
       </c>
-      <c r="BI21" s="235" t="s">
-        <v>2523</v>
-      </c>
-      <c r="BJ21" s="243" t="s">
+      <c r="BI21" s="229" t="s">
+        <v>2515</v>
+      </c>
+      <c r="BJ21" s="236" t="s">
         <v>2424</v>
       </c>
-      <c r="BK21" s="227" t="s">
+      <c r="BK21" s="224" t="s">
         <v>2080</v>
       </c>
-      <c r="BL21" s="256">
+      <c r="BL21" s="240">
         <v>89179</v>
       </c>
-      <c r="BM21" s="230" t="s">
+      <c r="BM21" s="226" t="s">
         <v>1597</v>
       </c>
-      <c r="BN21" s="227" t="s">
+      <c r="BN21" s="224" t="s">
         <v>1537</v>
       </c>
-      <c r="BO21" s="227" t="s">
+      <c r="BO21" s="224" t="s">
         <v>1537</v>
       </c>
-      <c r="BP21" s="227" t="s">
+      <c r="BP21" s="224" t="s">
         <v>1543</v>
       </c>
-      <c r="BQ21" s="230" t="s">
+      <c r="BQ21" s="226" t="s">
         <v>1583</v>
       </c>
-      <c r="BR21" s="232" t="s">
+      <c r="BR21" s="220" t="s">
         <v>1687</v>
       </c>
-      <c r="BS21" s="233" t="s">
+      <c r="BS21" s="228" t="s">
         <v>1545</v>
       </c>
-      <c r="BT21" s="232" t="s">
+      <c r="BT21" s="220" t="s">
         <v>1547</v>
       </c>
-      <c r="BU21" s="232" t="s">
+      <c r="BU21" s="220" t="s">
         <v>1551</v>
       </c>
-      <c r="BV21" s="232" t="s">
+      <c r="BV21" s="220" t="s">
         <v>1552</v>
       </c>
-      <c r="BW21" s="232" t="s">
+      <c r="BW21" s="220" t="s">
         <v>1523</v>
       </c>
-      <c r="BX21" s="232" t="s">
+      <c r="BX21" s="220" t="s">
         <v>1554</v>
       </c>
-      <c r="BY21" s="227" t="s">
+      <c r="BY21" s="224" t="s">
         <v>1556</v>
       </c>
-      <c r="BZ21" s="232" t="s">
+      <c r="BZ21" s="220" t="s">
         <v>1558</v>
       </c>
-      <c r="CA21" s="232" t="s">
+      <c r="CA21" s="220" t="s">
         <v>1565</v>
       </c>
-      <c r="CB21" s="232" t="s">
+      <c r="CB21" s="220" t="s">
         <v>1566</v>
       </c>
-      <c r="CC21" s="232" t="s">
+      <c r="CC21" s="220" t="s">
         <v>1567</v>
       </c>
-      <c r="CD21" s="232" t="s">
+      <c r="CD21" s="220" t="s">
         <v>1568</v>
       </c>
-      <c r="CF21" s="227" t="s">
+      <c r="CF21" s="224" t="s">
         <v>1629</v>
       </c>
-      <c r="CG21" s="227" t="s">
+      <c r="CG21" s="224" t="s">
         <v>1630</v>
       </c>
-      <c r="CH21" s="232" t="s">
+      <c r="CH21" s="220" t="s">
         <v>2332</v>
       </c>
-      <c r="CI21" s="232" t="s">
+      <c r="CI21" s="220" t="s">
         <v>1660</v>
       </c>
-      <c r="CJ21" s="244" t="s">
+      <c r="CJ21" s="237" t="s">
         <v>2226</v>
       </c>
-      <c r="CK21" s="234" t="s">
+      <c r="CK21" s="221" t="s">
         <v>2331</v>
       </c>
     </row>
-    <row r="22" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="22" spans="1:89" s="152" customFormat="1" ht="46.8" thickBot="1">
       <c r="A22" s="155" t="s">
         <v>2090</v>
       </c>
-      <c r="B22" s="213" t="s">
-        <v>2486</v>
+      <c r="B22" s="212" t="s">
+        <v>2530</v>
       </c>
       <c r="C22" s="152" t="s">
         <v>3</v>
@@ -13976,7 +13943,7 @@
         <v>2097</v>
       </c>
       <c r="AO22" s="191" t="s">
-        <v>2475</v>
+        <v>2472</v>
       </c>
       <c r="AP22" s="154" t="s">
         <v>2256</v>
@@ -13999,16 +13966,16 @@
       <c r="AV22" s="152" t="s">
         <v>2102</v>
       </c>
-      <c r="AW22" s="224">
+      <c r="AW22" s="221">
         <v>10466</v>
       </c>
       <c r="AX22" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY22" s="211"/>
-      <c r="AZ22" s="211"/>
-      <c r="BA22" s="211"/>
-      <c r="BB22" s="211"/>
+      <c r="AY22" s="191"/>
+      <c r="AZ22" s="191"/>
+      <c r="BA22" s="191"/>
+      <c r="BB22" s="191"/>
       <c r="BC22" s="154" t="s">
         <v>2103</v>
       </c>
@@ -14019,7 +13986,7 @@
         <v>2104</v>
       </c>
       <c r="BF22" s="208" t="s">
-        <v>2510</v>
+        <v>2502</v>
       </c>
       <c r="BG22" s="166" t="s">
         <v>2106</v>
@@ -14036,7 +14003,7 @@
       <c r="BK22" s="121" t="s">
         <v>2102</v>
       </c>
-      <c r="BL22" s="251">
+      <c r="BL22" s="120">
         <v>10466</v>
       </c>
       <c r="BM22" s="161" t="s">
@@ -14112,12 +14079,12 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="23" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="23" spans="1:89" s="152" customFormat="1" ht="47.4" thickBot="1">
       <c r="A23" s="155" t="s">
         <v>2113</v>
       </c>
-      <c r="B23" s="213" t="s">
-        <v>2487</v>
+      <c r="B23" s="212" t="s">
+        <v>2529</v>
       </c>
       <c r="C23" s="152" t="s">
         <v>3</v>
@@ -14193,7 +14160,7 @@
         <v>2120</v>
       </c>
       <c r="AO23" s="191" t="s">
-        <v>2518</v>
+        <v>2510</v>
       </c>
       <c r="AP23" s="154" t="s">
         <v>1652</v>
@@ -14216,16 +14183,16 @@
       <c r="AV23" s="152" t="s">
         <v>2125</v>
       </c>
-      <c r="AW23" s="224">
+      <c r="AW23" s="221">
         <v>97603</v>
       </c>
       <c r="AX23" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY23" s="211"/>
-      <c r="AZ23" s="211"/>
-      <c r="BA23" s="211"/>
-      <c r="BB23" s="211"/>
+      <c r="AY23" s="191"/>
+      <c r="AZ23" s="191"/>
+      <c r="BA23" s="191"/>
+      <c r="BB23" s="191"/>
       <c r="BC23" s="154" t="s">
         <v>2126</v>
       </c>
@@ -14236,7 +14203,7 @@
         <v>1964</v>
       </c>
       <c r="BF23" s="208" t="s">
-        <v>2511</v>
+        <v>2503</v>
       </c>
       <c r="BG23" s="166" t="s">
         <v>2128</v>
@@ -14253,7 +14220,7 @@
       <c r="BK23" s="196" t="s">
         <v>2125</v>
       </c>
-      <c r="BL23" s="251">
+      <c r="BL23" s="120">
         <v>97603</v>
       </c>
       <c r="BM23" s="161" t="s">
@@ -14329,12 +14296,12 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="24" spans="1:89" s="152" customFormat="1" ht="52" thickBot="1">
+    <row r="24" spans="1:89" s="152" customFormat="1" ht="46.8" thickBot="1">
       <c r="A24" s="155" t="s">
         <v>2136</v>
       </c>
-      <c r="B24" s="213" t="s">
-        <v>2488</v>
+      <c r="B24" s="212" t="s">
+        <v>2528</v>
       </c>
       <c r="C24" s="152" t="s">
         <v>3</v>
@@ -14410,7 +14377,7 @@
         <v>2142</v>
       </c>
       <c r="AO24" s="191" t="s">
-        <v>2465</v>
+        <v>2462</v>
       </c>
       <c r="AP24" s="154" t="s">
         <v>1652</v>
@@ -14433,16 +14400,16 @@
       <c r="AV24" s="152" t="s">
         <v>2147</v>
       </c>
-      <c r="AW24" s="224">
+      <c r="AW24" s="221">
         <v>19134</v>
       </c>
       <c r="AX24" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY24" s="211"/>
-      <c r="AZ24" s="211"/>
-      <c r="BA24" s="211"/>
-      <c r="BB24" s="211"/>
+      <c r="AY24" s="191"/>
+      <c r="AZ24" s="191"/>
+      <c r="BA24" s="191"/>
+      <c r="BB24" s="191"/>
       <c r="BC24" s="154" t="s">
         <v>2148</v>
       </c>
@@ -14453,7 +14420,7 @@
         <v>2149</v>
       </c>
       <c r="BF24" s="208" t="s">
-        <v>2512</v>
+        <v>2504</v>
       </c>
       <c r="BG24" s="166" t="s">
         <v>2150</v>
@@ -14470,7 +14437,7 @@
       <c r="BK24" s="121" t="s">
         <v>2147</v>
       </c>
-      <c r="BL24" s="251">
+      <c r="BL24" s="120">
         <v>19134</v>
       </c>
       <c r="BM24" s="161" t="s">
@@ -14546,12 +14513,12 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="25" spans="1:89" s="152" customFormat="1" ht="35" thickBot="1">
+    <row r="25" spans="1:89" s="152" customFormat="1" ht="46.8" thickBot="1">
       <c r="A25" s="155" t="s">
         <v>2158</v>
       </c>
-      <c r="B25" s="213" t="s">
-        <v>2489</v>
+      <c r="B25" s="212" t="s">
+        <v>2481</v>
       </c>
       <c r="C25" s="152" t="s">
         <v>3</v>
@@ -14627,7 +14594,7 @@
         <v>2164</v>
       </c>
       <c r="AO25" s="191" t="s">
-        <v>2476</v>
+        <v>2473</v>
       </c>
       <c r="AP25" s="154" t="s">
         <v>1652</v>
@@ -14650,16 +14617,16 @@
       <c r="AV25" s="152" t="s">
         <v>2169</v>
       </c>
-      <c r="AW25" s="224">
+      <c r="AW25" s="221">
         <v>57040</v>
       </c>
       <c r="AX25" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY25" s="211"/>
-      <c r="AZ25" s="211"/>
-      <c r="BA25" s="211"/>
-      <c r="BB25" s="211"/>
+      <c r="AY25" s="191"/>
+      <c r="AZ25" s="191"/>
+      <c r="BA25" s="191"/>
+      <c r="BB25" s="191"/>
       <c r="BC25" s="154" t="s">
         <v>2170</v>
       </c>
@@ -14687,7 +14654,7 @@
       <c r="BK25" s="121" t="s">
         <v>2169</v>
       </c>
-      <c r="BL25" s="251">
+      <c r="BL25" s="120">
         <v>57040</v>
       </c>
       <c r="BM25" s="161" t="s">
@@ -14763,12 +14730,12 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="26" spans="1:89" s="152" customFormat="1" ht="35" thickBot="1">
+    <row r="26" spans="1:89" s="152" customFormat="1" ht="46.2" thickBot="1">
       <c r="A26" s="155" t="s">
         <v>2180</v>
       </c>
-      <c r="B26" s="213" t="s">
-        <v>2490</v>
+      <c r="B26" s="212" t="s">
+        <v>2482</v>
       </c>
       <c r="C26" s="152" t="s">
         <v>3</v>
@@ -14844,7 +14811,7 @@
         <v>2187</v>
       </c>
       <c r="AO26" s="191" t="s">
-        <v>2477</v>
+        <v>2474</v>
       </c>
       <c r="AP26" s="154" t="s">
         <v>2256</v>
@@ -14867,16 +14834,16 @@
       <c r="AV26" s="152" t="s">
         <v>2192</v>
       </c>
-      <c r="AW26" s="224">
+      <c r="AW26" s="221">
         <v>37211</v>
       </c>
       <c r="AX26" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="AY26" s="211"/>
-      <c r="AZ26" s="211"/>
-      <c r="BA26" s="211"/>
-      <c r="BB26" s="211"/>
+      <c r="AY26" s="191"/>
+      <c r="AZ26" s="191"/>
+      <c r="BA26" s="191"/>
+      <c r="BB26" s="191"/>
       <c r="BC26" s="154" t="s">
         <v>2193</v>
       </c>
@@ -14887,7 +14854,7 @@
         <v>2194</v>
       </c>
       <c r="BF26" s="208" t="s">
-        <v>2513</v>
+        <v>2505</v>
       </c>
       <c r="BG26" s="166" t="s">
         <v>2195</v>
@@ -14904,7 +14871,7 @@
       <c r="BK26" s="152" t="s">
         <v>2192</v>
       </c>
-      <c r="BL26" s="251">
+      <c r="BL26" s="120">
         <v>37211</v>
       </c>
       <c r="BM26" s="161" t="s">
@@ -14980,12 +14947,12 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="27" spans="1:89" s="176" customFormat="1" ht="52" thickBot="1">
+    <row r="27" spans="1:89" s="176" customFormat="1" ht="46.2" thickBot="1">
       <c r="A27" s="174" t="s">
         <v>2202</v>
       </c>
-      <c r="B27" s="214" t="s">
-        <v>2491</v>
+      <c r="B27" s="213" t="s">
+        <v>2483</v>
       </c>
       <c r="C27" s="176" t="s">
         <v>3</v>
@@ -15086,7 +15053,7 @@
         <v>2209</v>
       </c>
       <c r="AO27" s="191" t="s">
-        <v>2466</v>
+        <v>2463</v>
       </c>
       <c r="AP27" s="184" t="s">
         <v>1652</v>
@@ -15109,16 +15076,16 @@
       <c r="AV27" s="176" t="s">
         <v>2214</v>
       </c>
-      <c r="AW27" s="222">
+      <c r="AW27" s="219">
         <v>77845</v>
       </c>
       <c r="AX27" s="177" t="s">
         <v>1597</v>
       </c>
-      <c r="AY27" s="212"/>
-      <c r="AZ27" s="212"/>
-      <c r="BA27" s="212"/>
-      <c r="BB27" s="212"/>
+      <c r="AY27" s="211"/>
+      <c r="AZ27" s="211"/>
+      <c r="BA27" s="211"/>
+      <c r="BB27" s="211"/>
       <c r="BC27" s="184" t="s">
         <v>2215</v>
       </c>
@@ -15129,7 +15096,7 @@
         <v>2216</v>
       </c>
       <c r="BF27" s="208" t="s">
-        <v>2514</v>
+        <v>2506</v>
       </c>
       <c r="BG27" s="185" t="s">
         <v>2217</v>
@@ -15146,7 +15113,7 @@
       <c r="BK27" s="176" t="s">
         <v>2214</v>
       </c>
-      <c r="BL27" s="250">
+      <c r="BL27" s="122">
         <v>77845</v>
       </c>
       <c r="BM27" s="181" t="s">
@@ -15164,10 +15131,10 @@
       <c r="BQ27" s="177" t="s">
         <v>1583</v>
       </c>
-      <c r="BR27" s="217" t="s">
+      <c r="BR27" s="140" t="s">
         <v>1687</v>
       </c>
-      <c r="BS27" s="218" t="s">
+      <c r="BS27" s="142" t="s">
         <v>1545</v>
       </c>
       <c r="BT27" s="179" t="s">
@@ -15222,12 +15189,12 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="28" spans="1:89" s="176" customFormat="1" ht="18" thickBot="1">
+    <row r="28" spans="1:89" s="176" customFormat="1" ht="16.2" thickBot="1">
       <c r="A28" s="174" t="s">
         <v>2224</v>
       </c>
-      <c r="B28" s="214" t="s">
-        <v>2492</v>
+      <c r="B28" s="213" t="s">
+        <v>2484</v>
       </c>
       <c r="C28" s="176" t="s">
         <v>3</v>
@@ -15328,7 +15295,7 @@
         <v>2272</v>
       </c>
       <c r="AO28" s="191" t="s">
-        <v>2478</v>
+        <v>2475</v>
       </c>
       <c r="AP28" s="184" t="s">
         <v>1652</v>
@@ -15351,16 +15318,16 @@
       <c r="AV28" s="187" t="s">
         <v>2382</v>
       </c>
-      <c r="AW28" s="225">
+      <c r="AW28" s="222">
         <v>23454</v>
       </c>
       <c r="AX28" s="177" t="s">
         <v>1597</v>
       </c>
-      <c r="AY28" s="212"/>
-      <c r="AZ28" s="212"/>
-      <c r="BA28" s="212"/>
-      <c r="BB28" s="212"/>
+      <c r="AY28" s="211"/>
+      <c r="AZ28" s="211"/>
+      <c r="BA28" s="211"/>
+      <c r="BB28" s="211"/>
       <c r="BC28" s="184" t="s">
         <v>2383</v>
       </c>
@@ -15371,7 +15338,7 @@
         <v>2384</v>
       </c>
       <c r="BF28" s="208" t="s">
-        <v>2515</v>
+        <v>2507</v>
       </c>
       <c r="BG28" s="184" t="s">
         <v>2385</v>
@@ -15388,7 +15355,7 @@
       <c r="BK28" s="176" t="s">
         <v>2080</v>
       </c>
-      <c r="BL28" s="250">
+      <c r="BL28" s="122">
         <v>89115</v>
       </c>
       <c r="BM28" s="181" t="s">
@@ -15406,10 +15373,10 @@
       <c r="BQ28" s="177" t="s">
         <v>1583</v>
       </c>
-      <c r="BR28" s="217" t="s">
+      <c r="BR28" s="140" t="s">
         <v>1687</v>
       </c>
-      <c r="BS28" s="218" t="s">
+      <c r="BS28" s="142" t="s">
         <v>1545</v>
       </c>
       <c r="BT28" s="179" t="s">
@@ -15485,36 +15452,36 @@
     <hyperlink ref="D20" r:id="rId17" display="testpurchasesingleborrwer+devsp22@gmail.com" xr:uid="{3CD4A87D-A071-FD4A-983D-B7C4286FD480}"/>
     <hyperlink ref="D27" r:id="rId18" display="testpurchasesingleborrwer+devsp22@gmail.com" xr:uid="{5343DFF2-CC68-8943-966D-7FDDB4EDFA5D}"/>
     <hyperlink ref="D4" r:id="rId19" display="testpurchasesingleborrwer+devsp22@gmail.com" xr:uid="{C7AB4028-0380-E149-9DD0-728675C98220}"/>
-    <hyperlink ref="B4" r:id="rId20" xr:uid="{BD339301-3BC8-1943-A1F5-94AC243B0125}"/>
-    <hyperlink ref="D28" r:id="rId21" display="testpurchasesingleborrwer+devsp22@gmail.com" xr:uid="{BF8CBA4C-3D5F-9945-A19F-7E55480D38AC}"/>
-    <hyperlink ref="D21:D26" r:id="rId22" display="testpurchasesingleborrwer+devsp22@gmail.com" xr:uid="{D1E958E6-B19E-994D-8DE8-A06B076965E3}"/>
-    <hyperlink ref="D16" r:id="rId23" display="testpurchasesingleborrwer+devsp22@gmail.com" xr:uid="{BF49549A-9432-2C4B-894D-FDECAC393220}"/>
-    <hyperlink ref="B5" r:id="rId24" xr:uid="{C5A31089-B8FC-2047-8ED7-A8E143C8ADBC}"/>
-    <hyperlink ref="B6" r:id="rId25" xr:uid="{268DB0D0-0A9F-8B46-9EBA-CB67CA4EFC98}"/>
-    <hyperlink ref="B7" r:id="rId26" xr:uid="{92CA93CE-CA47-EB46-AD22-3E5B5BD31312}"/>
-    <hyperlink ref="B8" r:id="rId27" xr:uid="{8954E877-771A-D248-BABF-40AE856CC672}"/>
-    <hyperlink ref="B9" r:id="rId28" xr:uid="{2AA47D77-EE9B-7A48-8E89-4DA4B6AA7DED}"/>
-    <hyperlink ref="B13" r:id="rId29" xr:uid="{B5E8DA67-0A8A-F043-B668-17F2F5F59A07}"/>
-    <hyperlink ref="B14" r:id="rId30" xr:uid="{5149B59E-CBF4-C44A-A237-C29F68F0EC27}"/>
-    <hyperlink ref="B19" r:id="rId31" xr:uid="{E2132B68-DB84-BE4E-82DE-A29A0FDA3E6F}"/>
-    <hyperlink ref="B20" r:id="rId32" xr:uid="{F623ED6B-B900-3B49-91CC-AB452D09DFD9}"/>
-    <hyperlink ref="B21" r:id="rId33" xr:uid="{AC80FA6D-E531-5945-BA3F-F63793E0B00A}"/>
-    <hyperlink ref="B22" r:id="rId34" xr:uid="{E0960104-192E-9741-BBFF-85117C269308}"/>
-    <hyperlink ref="B23" r:id="rId35" xr:uid="{C469C9F9-2BF4-154B-B112-3F8FFC05B3E9}"/>
-    <hyperlink ref="B24" r:id="rId36" xr:uid="{55AE80E8-45B7-FC42-B4E0-9B257EEB56A6}"/>
-    <hyperlink ref="B25" r:id="rId37" xr:uid="{1292F6D7-C33A-474B-92B1-84D7199BAFE7}"/>
-    <hyperlink ref="B26" r:id="rId38" xr:uid="{3422E0AC-F913-1F4A-A149-CE967153C269}"/>
-    <hyperlink ref="B27" r:id="rId39" xr:uid="{EAE5736F-F210-834C-9184-D867A50BA21F}"/>
-    <hyperlink ref="B28" r:id="rId40" xr:uid="{CD71769C-37C9-F341-901E-F344CA0BEA22}"/>
-    <hyperlink ref="B15" r:id="rId41" xr:uid="{5C7DAA2E-92EE-2244-BA6D-A0BEB3AD68A4}"/>
-    <hyperlink ref="B16" r:id="rId42" xr:uid="{0A323E5B-3E19-C041-80D6-1145FCC69067}"/>
-    <hyperlink ref="B17" r:id="rId43" xr:uid="{65E2CFB3-2458-934B-A653-AECF3E76DBD9}"/>
-    <hyperlink ref="B18" r:id="rId44" xr:uid="{A8B1DF86-F0D1-A848-8467-7F899666CD67}"/>
-    <hyperlink ref="B2" r:id="rId45" xr:uid="{6032930E-35BE-6A47-B67E-7BBA1B089FFE}"/>
-    <hyperlink ref="B3" r:id="rId46" xr:uid="{5A1E00EC-6FC4-7042-B8B6-62D6E9C77E98}"/>
-    <hyperlink ref="B10" r:id="rId47" xr:uid="{2A486D9B-0C75-0145-9414-664FC6885EA4}"/>
-    <hyperlink ref="B11" r:id="rId48" xr:uid="{795E8BEC-F79E-CC48-B350-446B2E11A6C2}"/>
-    <hyperlink ref="B12" r:id="rId49" xr:uid="{147E2259-EA10-064C-8ACD-3C75881320F1}"/>
+    <hyperlink ref="D28" r:id="rId20" display="testpurchasesingleborrwer+devsp22@gmail.com" xr:uid="{BF8CBA4C-3D5F-9945-A19F-7E55480D38AC}"/>
+    <hyperlink ref="D21:D26" r:id="rId21" display="testpurchasesingleborrwer+devsp22@gmail.com" xr:uid="{D1E958E6-B19E-994D-8DE8-A06B076965E3}"/>
+    <hyperlink ref="D16" r:id="rId22" display="testpurchasesingleborrwer+devsp22@gmail.com" xr:uid="{BF49549A-9432-2C4B-894D-FDECAC393220}"/>
+    <hyperlink ref="B6" r:id="rId23" xr:uid="{268DB0D0-0A9F-8B46-9EBA-CB67CA4EFC98}"/>
+    <hyperlink ref="B7" r:id="rId24" xr:uid="{92CA93CE-CA47-EB46-AD22-3E5B5BD31312}"/>
+    <hyperlink ref="B8" r:id="rId25" xr:uid="{8954E877-771A-D248-BABF-40AE856CC672}"/>
+    <hyperlink ref="B9" r:id="rId26" xr:uid="{2AA47D77-EE9B-7A48-8E89-4DA4B6AA7DED}"/>
+    <hyperlink ref="B13" r:id="rId27" xr:uid="{B5E8DA67-0A8A-F043-B668-17F2F5F59A07}"/>
+    <hyperlink ref="B14" r:id="rId28" xr:uid="{5149B59E-CBF4-C44A-A237-C29F68F0EC27}"/>
+    <hyperlink ref="B19" r:id="rId29" xr:uid="{E2132B68-DB84-BE4E-82DE-A29A0FDA3E6F}"/>
+    <hyperlink ref="B20" r:id="rId30" xr:uid="{F623ED6B-B900-3B49-91CC-AB452D09DFD9}"/>
+    <hyperlink ref="B23" r:id="rId31" xr:uid="{C469C9F9-2BF4-154B-B112-3F8FFC05B3E9}"/>
+    <hyperlink ref="B24" r:id="rId32" xr:uid="{55AE80E8-45B7-FC42-B4E0-9B257EEB56A6}"/>
+    <hyperlink ref="B25" r:id="rId33" xr:uid="{1292F6D7-C33A-474B-92B1-84D7199BAFE7}"/>
+    <hyperlink ref="B26" r:id="rId34" xr:uid="{3422E0AC-F913-1F4A-A149-CE967153C269}"/>
+    <hyperlink ref="B27" r:id="rId35" xr:uid="{EAE5736F-F210-834C-9184-D867A50BA21F}"/>
+    <hyperlink ref="B28" r:id="rId36" xr:uid="{CD71769C-37C9-F341-901E-F344CA0BEA22}"/>
+    <hyperlink ref="B15" r:id="rId37" xr:uid="{5C7DAA2E-92EE-2244-BA6D-A0BEB3AD68A4}"/>
+    <hyperlink ref="B16" r:id="rId38" xr:uid="{0A323E5B-3E19-C041-80D6-1145FCC69067}"/>
+    <hyperlink ref="B17" r:id="rId39" xr:uid="{65E2CFB3-2458-934B-A653-AECF3E76DBD9}"/>
+    <hyperlink ref="B18" r:id="rId40" xr:uid="{A8B1DF86-F0D1-A848-8467-7F899666CD67}"/>
+    <hyperlink ref="B2" r:id="rId41" xr:uid="{6032930E-35BE-6A47-B67E-7BBA1B089FFE}"/>
+    <hyperlink ref="B3" r:id="rId42" xr:uid="{5A1E00EC-6FC4-7042-B8B6-62D6E9C77E98}"/>
+    <hyperlink ref="B10" r:id="rId43" xr:uid="{2A486D9B-0C75-0145-9414-664FC6885EA4}"/>
+    <hyperlink ref="B11" r:id="rId44" xr:uid="{795E8BEC-F79E-CC48-B350-446B2E11A6C2}"/>
+    <hyperlink ref="B12" r:id="rId45" xr:uid="{147E2259-EA10-064C-8ACD-3C75881320F1}"/>
+    <hyperlink ref="B4" r:id="rId46" xr:uid="{F257AC88-7AA5-4938-84D4-D99FA90A5CA2}"/>
+    <hyperlink ref="B5" r:id="rId47" xr:uid="{904FA78C-0580-447C-8D0C-A842F6DE2521}"/>
+    <hyperlink ref="B22" r:id="rId48" xr:uid="{E0960104-192E-9741-BBFF-85117C269308}"/>
+    <hyperlink ref="B21" r:id="rId49" xr:uid="{AC80FA6D-E531-5945-BA3F-F63793E0B00A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15523,16 +15490,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0C6CE9B-CD34-5D48-B6FB-B25F5320CF68}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.5" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="117" t="s">
         <v>2278</v>
       </c>
@@ -16016,53 +15983,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA3C18A-1977-F144-8CC5-0E17784FEFDF}">
   <dimension ref="A1:CC28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" style="41" customWidth="1"/>
-    <col min="2" max="2" width="57.1640625" style="41" customWidth="1"/>
+    <col min="1" max="1" width="24.109375" style="41" customWidth="1"/>
+    <col min="2" max="2" width="57.109375" style="41" customWidth="1"/>
     <col min="3" max="5" width="13.6640625" style="41" customWidth="1"/>
-    <col min="6" max="6" width="17.5" style="41" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" style="41" customWidth="1"/>
     <col min="7" max="7" width="20.33203125" style="41" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="41" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" style="41" customWidth="1"/>
     <col min="9" max="9" width="16" style="41" customWidth="1"/>
     <col min="10" max="10" width="22.6640625" style="41" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="41" customWidth="1"/>
-    <col min="12" max="12" width="30.83203125" style="41" customWidth="1"/>
-    <col min="13" max="13" width="13.83203125" style="41" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" style="41" customWidth="1"/>
+    <col min="12" max="12" width="30.77734375" style="41" customWidth="1"/>
+    <col min="13" max="13" width="13.77734375" style="41" customWidth="1"/>
     <col min="14" max="14" width="16.6640625" style="41" customWidth="1"/>
-    <col min="15" max="15" width="18.83203125" style="41" customWidth="1"/>
-    <col min="16" max="16" width="16.83203125" style="41" customWidth="1"/>
-    <col min="17" max="17" width="15.83203125" style="41" customWidth="1"/>
+    <col min="15" max="15" width="18.77734375" style="41" customWidth="1"/>
+    <col min="16" max="16" width="16.77734375" style="41" customWidth="1"/>
+    <col min="17" max="17" width="15.77734375" style="41" customWidth="1"/>
     <col min="18" max="33" width="14.6640625" style="41" customWidth="1"/>
-    <col min="34" max="35" width="20.5" style="41" customWidth="1"/>
-    <col min="36" max="36" width="18.1640625" style="41" customWidth="1"/>
-    <col min="37" max="37" width="16.83203125" style="41" customWidth="1"/>
-    <col min="38" max="39" width="12.5" style="41" customWidth="1"/>
-    <col min="40" max="40" width="25.5" style="41" customWidth="1"/>
-    <col min="41" max="41" width="12.5" style="41" customWidth="1"/>
+    <col min="34" max="35" width="20.44140625" style="41" customWidth="1"/>
+    <col min="36" max="36" width="18.109375" style="41" customWidth="1"/>
+    <col min="37" max="37" width="16.77734375" style="41" customWidth="1"/>
+    <col min="38" max="39" width="12.44140625" style="41" customWidth="1"/>
+    <col min="40" max="40" width="25.44140625" style="41" customWidth="1"/>
+    <col min="41" max="41" width="12.44140625" style="41" customWidth="1"/>
     <col min="42" max="42" width="37.33203125" style="41" customWidth="1"/>
     <col min="43" max="43" width="49.33203125" style="41" customWidth="1"/>
-    <col min="44" max="44" width="39.5" style="41" customWidth="1"/>
-    <col min="45" max="45" width="27.83203125" style="41" customWidth="1"/>
-    <col min="46" max="47" width="8.83203125" style="41"/>
-    <col min="48" max="48" width="28.5" style="41" customWidth="1"/>
+    <col min="44" max="44" width="39.44140625" style="41" customWidth="1"/>
+    <col min="45" max="45" width="27.77734375" style="41" customWidth="1"/>
+    <col min="46" max="47" width="8.77734375" style="41"/>
+    <col min="48" max="48" width="28.44140625" style="41" customWidth="1"/>
     <col min="49" max="49" width="33.6640625" style="41" customWidth="1"/>
-    <col min="50" max="50" width="27.5" style="41" customWidth="1"/>
-    <col min="51" max="51" width="30.5" style="41" customWidth="1"/>
-    <col min="52" max="57" width="21.5" style="41" customWidth="1"/>
-    <col min="58" max="58" width="22.1640625" style="41" customWidth="1"/>
-    <col min="59" max="60" width="8.83203125" style="41"/>
-    <col min="61" max="61" width="13.1640625" style="41" customWidth="1"/>
-    <col min="62" max="74" width="8.83203125" style="41"/>
-    <col min="75" max="76" width="15.1640625" style="41" customWidth="1"/>
-    <col min="77" max="77" width="16.1640625" style="41" customWidth="1"/>
-    <col min="78" max="79" width="8.83203125" style="41"/>
-    <col min="80" max="80" width="18.83203125" style="41" customWidth="1"/>
-    <col min="81" max="81" width="17.1640625" style="41" customWidth="1"/>
-    <col min="82" max="16384" width="8.83203125" style="41"/>
+    <col min="50" max="50" width="27.44140625" style="41" customWidth="1"/>
+    <col min="51" max="51" width="30.44140625" style="41" customWidth="1"/>
+    <col min="52" max="57" width="21.44140625" style="41" customWidth="1"/>
+    <col min="58" max="58" width="22.109375" style="41" customWidth="1"/>
+    <col min="59" max="60" width="8.77734375" style="41"/>
+    <col min="61" max="61" width="13.109375" style="41" customWidth="1"/>
+    <col min="62" max="74" width="8.77734375" style="41"/>
+    <col min="75" max="76" width="15.109375" style="41" customWidth="1"/>
+    <col min="77" max="77" width="16.109375" style="41" customWidth="1"/>
+    <col min="78" max="79" width="8.77734375" style="41"/>
+    <col min="80" max="80" width="18.77734375" style="41" customWidth="1"/>
+    <col min="81" max="81" width="17.109375" style="41" customWidth="1"/>
+    <col min="82" max="16384" width="8.77734375" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" s="66" customFormat="1" ht="14">
+    <row r="1" spans="1:81" s="66" customFormat="1" ht="13.8">
       <c r="A1" s="58" t="s">
         <v>1633</v>
       </c>
@@ -16295,7 +16262,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="2" spans="1:81" ht="32" thickBot="1">
+    <row r="2" spans="1:81" ht="28.8" thickBot="1">
       <c r="A2" s="67" t="s">
         <v>1663</v>
       </c>
@@ -16528,7 +16495,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="3" spans="1:81" ht="47" thickBot="1">
+    <row r="3" spans="1:81" ht="42.6" thickBot="1">
       <c r="A3" s="67" t="s">
         <v>1677</v>
       </c>
@@ -16761,7 +16728,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="4" spans="1:81" ht="47" thickBot="1">
+    <row r="4" spans="1:81" ht="42.6" thickBot="1">
       <c r="A4" s="67" t="s">
         <v>1693</v>
       </c>
@@ -16994,7 +16961,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="5" spans="1:81" ht="47" thickBot="1">
+    <row r="5" spans="1:81" ht="42.6" thickBot="1">
       <c r="A5" s="67" t="s">
         <v>1716</v>
       </c>
@@ -17227,7 +17194,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="6" spans="1:81" ht="47" thickBot="1">
+    <row r="6" spans="1:81" ht="56.4" thickBot="1">
       <c r="A6" s="67" t="s">
         <v>1739</v>
       </c>
@@ -17458,7 +17425,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="7" spans="1:81" ht="47" thickBot="1">
+    <row r="7" spans="1:81" ht="42.6" thickBot="1">
       <c r="A7" s="67" t="s">
         <v>1761</v>
       </c>
@@ -17689,7 +17656,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="8" spans="1:81" ht="47" thickBot="1">
+    <row r="8" spans="1:81" ht="42.6" thickBot="1">
       <c r="A8" s="67" t="s">
         <v>1784</v>
       </c>
@@ -17920,7 +17887,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="9" spans="1:81" ht="47" thickBot="1">
+    <row r="9" spans="1:81" ht="42.6" thickBot="1">
       <c r="A9" s="67" t="s">
         <v>1807</v>
       </c>
@@ -18151,7 +18118,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="10" spans="1:81" ht="47" thickBot="1">
+    <row r="10" spans="1:81" ht="42.6" thickBot="1">
       <c r="A10" s="67" t="s">
         <v>1829</v>
       </c>
@@ -18380,7 +18347,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="11" spans="1:81" ht="47" thickBot="1">
+    <row r="11" spans="1:81" ht="42.6" thickBot="1">
       <c r="A11" s="67" t="s">
         <v>1850</v>
       </c>
@@ -18611,7 +18578,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="12" spans="1:81" ht="47" thickBot="1">
+    <row r="12" spans="1:81" ht="42.6" thickBot="1">
       <c r="A12" s="67" t="s">
         <v>1872</v>
       </c>
@@ -18842,7 +18809,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="13" spans="1:81" ht="47" thickBot="1">
+    <row r="13" spans="1:81" ht="42.6" thickBot="1">
       <c r="A13" s="67" t="s">
         <v>1893</v>
       </c>
@@ -19073,7 +19040,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="14" spans="1:81" ht="62" thickBot="1">
+    <row r="14" spans="1:81" ht="56.4" thickBot="1">
       <c r="A14" s="67" t="s">
         <v>1915</v>
       </c>
@@ -19304,7 +19271,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="15" spans="1:81" ht="47" thickBot="1">
+    <row r="15" spans="1:81" ht="42.6" thickBot="1">
       <c r="A15" s="67" t="s">
         <v>1936</v>
       </c>
@@ -19535,7 +19502,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="16" spans="1:81" ht="47" thickBot="1">
+    <row r="16" spans="1:81" ht="42.6" thickBot="1">
       <c r="A16" s="67" t="s">
         <v>1958</v>
       </c>
@@ -19768,7 +19735,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="17" spans="1:81" ht="47" thickBot="1">
+    <row r="17" spans="1:81" ht="42.6" thickBot="1">
       <c r="A17" s="67" t="s">
         <v>1979</v>
       </c>
@@ -19999,7 +19966,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="18" spans="1:81" ht="32" thickBot="1">
+    <row r="18" spans="1:81" ht="42.6" thickBot="1">
       <c r="A18" s="67" t="s">
         <v>2000</v>
       </c>
@@ -20230,7 +20197,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="19" spans="1:81" ht="47" thickBot="1">
+    <row r="19" spans="1:81" ht="42.6" thickBot="1">
       <c r="A19" s="67" t="s">
         <v>2022</v>
       </c>
@@ -20461,7 +20428,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="20" spans="1:81" ht="47" thickBot="1">
+    <row r="20" spans="1:81" ht="42.6" thickBot="1">
       <c r="A20" s="67" t="s">
         <v>2044</v>
       </c>
@@ -20694,7 +20661,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="21" spans="1:81" ht="47" thickBot="1">
+    <row r="21" spans="1:81" ht="42.6" thickBot="1">
       <c r="A21" s="67" t="s">
         <v>2068</v>
       </c>
@@ -20927,7 +20894,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="22" spans="1:81" ht="47" thickBot="1">
+    <row r="22" spans="1:81" ht="42.6" thickBot="1">
       <c r="A22" s="67" t="s">
         <v>2090</v>
       </c>
@@ -21160,7 +21127,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="23" spans="1:81" ht="47" thickBot="1">
+    <row r="23" spans="1:81" ht="42.6" thickBot="1">
       <c r="A23" s="67" t="s">
         <v>2113</v>
       </c>
@@ -21393,7 +21360,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="24" spans="1:81" ht="47" thickBot="1">
+    <row r="24" spans="1:81" ht="42.6" thickBot="1">
       <c r="A24" s="67" t="s">
         <v>2136</v>
       </c>
@@ -21626,7 +21593,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="25" spans="1:81" ht="47" thickBot="1">
+    <row r="25" spans="1:81" ht="42.6" thickBot="1">
       <c r="A25" s="67" t="s">
         <v>2158</v>
       </c>
@@ -21859,7 +21826,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="26" spans="1:81" ht="47" thickBot="1">
+    <row r="26" spans="1:81" ht="42.6" thickBot="1">
       <c r="A26" s="67" t="s">
         <v>2180</v>
       </c>
@@ -22092,7 +22059,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="27" spans="1:81" ht="47" thickBot="1">
+    <row r="27" spans="1:81" ht="42.6" thickBot="1">
       <c r="A27" s="67" t="s">
         <v>2202</v>
       </c>
@@ -22325,7 +22292,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="28" spans="1:81" ht="47" thickBot="1">
+    <row r="28" spans="1:81" ht="42.6" thickBot="1">
       <c r="A28" s="67" t="s">
         <v>2224</v>
       </c>
@@ -22600,12 +22567,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2321C6A4-AD00-42A6-92A5-5BEB8B613463}">
   <dimension ref="A1:CC2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="38" max="38" width="14.83203125" customWidth="1"/>
+    <col min="38" max="38" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" s="66" customFormat="1" ht="14">
+    <row r="1" spans="1:81" s="66" customFormat="1" ht="13.8">
       <c r="A1" s="58" t="s">
         <v>1633</v>
       </c>
@@ -22838,7 +22805,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="2" spans="1:81" s="41" customFormat="1" ht="46">
+    <row r="2" spans="1:81" s="41" customFormat="1" ht="42">
       <c r="A2" s="67" t="s">
         <v>1639</v>
       </c>
@@ -23084,45 +23051,45 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67973E72-2C1E-43CF-8083-F8643182AC98}">
   <dimension ref="A1:BQ2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44.6640625" customWidth="1"/>
     <col min="2" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
     <col min="6" max="6" width="20.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="22.6640625" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.77734375" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" customWidth="1"/>
+    <col min="12" max="12" width="13.77734375" customWidth="1"/>
     <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="18.83203125" customWidth="1"/>
-    <col min="15" max="15" width="16.83203125" customWidth="1"/>
-    <col min="16" max="16" width="15.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.77734375" customWidth="1"/>
+    <col min="15" max="15" width="16.77734375" customWidth="1"/>
+    <col min="16" max="16" width="15.77734375" customWidth="1"/>
     <col min="17" max="26" width="14.6640625" customWidth="1"/>
-    <col min="27" max="28" width="20.5" customWidth="1"/>
-    <col min="29" max="29" width="18.1640625" customWidth="1"/>
-    <col min="30" max="30" width="16.83203125" customWidth="1"/>
-    <col min="31" max="31" width="12.5" customWidth="1"/>
-    <col min="32" max="32" width="25.5" customWidth="1"/>
-    <col min="33" max="33" width="12.5" customWidth="1"/>
+    <col min="27" max="28" width="20.44140625" customWidth="1"/>
+    <col min="29" max="29" width="18.109375" customWidth="1"/>
+    <col min="30" max="30" width="16.77734375" customWidth="1"/>
+    <col min="31" max="31" width="12.44140625" customWidth="1"/>
+    <col min="32" max="32" width="25.44140625" customWidth="1"/>
+    <col min="33" max="33" width="12.44140625" customWidth="1"/>
     <col min="34" max="34" width="37.33203125" customWidth="1"/>
     <col min="35" max="35" width="49.33203125" customWidth="1"/>
-    <col min="36" max="36" width="39.5" customWidth="1"/>
-    <col min="37" max="37" width="27.83203125" customWidth="1"/>
-    <col min="40" max="40" width="28.5" customWidth="1"/>
+    <col min="36" max="36" width="39.44140625" customWidth="1"/>
+    <col min="37" max="37" width="27.77734375" customWidth="1"/>
+    <col min="40" max="40" width="28.44140625" customWidth="1"/>
     <col min="41" max="41" width="33.6640625" customWidth="1"/>
-    <col min="42" max="42" width="27.5" customWidth="1"/>
-    <col min="43" max="43" width="30.5" customWidth="1"/>
-    <col min="44" max="49" width="21.5" customWidth="1"/>
-    <col min="50" max="50" width="22.1640625" customWidth="1"/>
-    <col min="53" max="53" width="13.1640625" customWidth="1"/>
-    <col min="67" max="68" width="15.1640625" customWidth="1"/>
-    <col min="69" max="69" width="16.1640625" customWidth="1"/>
+    <col min="42" max="42" width="27.44140625" customWidth="1"/>
+    <col min="43" max="43" width="30.44140625" customWidth="1"/>
+    <col min="44" max="49" width="21.44140625" customWidth="1"/>
+    <col min="50" max="50" width="22.109375" customWidth="1"/>
+    <col min="53" max="53" width="13.109375" customWidth="1"/>
+    <col min="67" max="68" width="15.109375" customWidth="1"/>
+    <col min="69" max="69" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" s="57" customFormat="1" ht="21.5" customHeight="1">
+    <row r="1" spans="1:69" s="57" customFormat="1" ht="21.45" customHeight="1">
       <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
@@ -23554,44 +23521,44 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F73698-D2CA-4C80-97AC-0F3A7BDDB95D}">
   <dimension ref="A1:BO2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="22.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" customWidth="1"/>
-    <col min="14" max="14" width="15.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" customWidth="1"/>
+    <col min="13" max="13" width="16.77734375" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" customWidth="1"/>
     <col min="15" max="24" width="14.6640625" customWidth="1"/>
-    <col min="25" max="26" width="20.5" customWidth="1"/>
-    <col min="27" max="27" width="18.1640625" customWidth="1"/>
-    <col min="28" max="28" width="16.83203125" customWidth="1"/>
-    <col min="29" max="29" width="12.5" customWidth="1"/>
-    <col min="30" max="30" width="25.5" customWidth="1"/>
-    <col min="31" max="31" width="12.5" customWidth="1"/>
+    <col min="25" max="26" width="20.44140625" customWidth="1"/>
+    <col min="27" max="27" width="18.109375" customWidth="1"/>
+    <col min="28" max="28" width="16.77734375" customWidth="1"/>
+    <col min="29" max="29" width="12.44140625" customWidth="1"/>
+    <col min="30" max="30" width="25.44140625" customWidth="1"/>
+    <col min="31" max="31" width="12.44140625" customWidth="1"/>
     <col min="32" max="32" width="37.33203125" customWidth="1"/>
     <col min="33" max="33" width="49.33203125" customWidth="1"/>
-    <col min="34" max="34" width="39.5" customWidth="1"/>
-    <col min="35" max="35" width="27.83203125" customWidth="1"/>
-    <col min="38" max="38" width="28.5" customWidth="1"/>
+    <col min="34" max="34" width="39.44140625" customWidth="1"/>
+    <col min="35" max="35" width="27.77734375" customWidth="1"/>
+    <col min="38" max="38" width="28.44140625" customWidth="1"/>
     <col min="39" max="39" width="33.6640625" customWidth="1"/>
-    <col min="40" max="40" width="27.5" customWidth="1"/>
-    <col min="41" max="41" width="30.5" customWidth="1"/>
-    <col min="42" max="47" width="21.5" customWidth="1"/>
-    <col min="48" max="48" width="22.1640625" customWidth="1"/>
-    <col min="51" max="51" width="13.1640625" customWidth="1"/>
-    <col min="65" max="66" width="15.1640625" customWidth="1"/>
-    <col min="67" max="67" width="16.1640625" customWidth="1"/>
+    <col min="40" max="40" width="27.44140625" customWidth="1"/>
+    <col min="41" max="41" width="30.44140625" customWidth="1"/>
+    <col min="42" max="47" width="21.44140625" customWidth="1"/>
+    <col min="48" max="48" width="22.109375" customWidth="1"/>
+    <col min="51" max="51" width="13.109375" customWidth="1"/>
+    <col min="65" max="66" width="15.109375" customWidth="1"/>
+    <col min="67" max="67" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" s="57" customFormat="1" ht="21.5" customHeight="1">
+    <row r="1" spans="1:67" s="57" customFormat="1" ht="21.45" customHeight="1">
       <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
@@ -24010,11 +23977,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3946C45-EBB5-4252-B621-2FCDA30E8C12}">
   <dimension ref="A1:AS2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="44" max="44" width="30.5" customWidth="1"/>
+    <col min="1" max="1" width="52.77734375" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="44" max="44" width="30.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45">
@@ -24297,20 +24264,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AS2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="53.1640625" customWidth="1"/>
+    <col min="1" max="1" width="53.109375" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1"/>
     <col min="13" max="13" width="21.33203125" customWidth="1"/>
-    <col min="18" max="18" width="18.1640625" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
-    <col min="20" max="20" width="12.5" customWidth="1"/>
+    <col min="18" max="18" width="18.109375" customWidth="1"/>
+    <col min="19" max="19" width="16.77734375" customWidth="1"/>
+    <col min="20" max="20" width="12.44140625" customWidth="1"/>
     <col min="21" max="21" width="24" customWidth="1"/>
     <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
     <col min="44" max="45" width="10" bestFit="1" customWidth="1"/>
@@ -24597,7 +24564,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{897DFC33-19EE-4480-80FF-E3D84987520C}">
   <dimension ref="A1:AN2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:40">
       <c r="A1" s="1" t="s">
@@ -24855,7 +24822,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37407760-DC9B-4475-8441-CBEF2507273E}">
   <dimension ref="A1:BEG1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:1489">
       <c r="A1" t="s">
